--- a/TEMPLATE PENGUAPAN.xlsx
+++ b/TEMPLATE PENGUAPAN.xlsx
@@ -152,11 +152,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="0.0"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;Rp&quot;* #,##0.00_-;\-&quot;Rp&quot;* #,##0.00_-;_-&quot;Rp&quot;* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_(&quot;Rp&quot;* #,##0_);_(&quot;Rp&quot;* \(#,##0\);_(&quot;Rp&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="177" formatCode="0.0"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;Rp&quot;* #,##0_-;\-&quot;Rp&quot;* #,##0_-;_-&quot;Rp&quot;* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;Rp&quot;* #,##0.00_-;\-&quot;Rp&quot;* #,##0.00_-;_-&quot;Rp&quot;* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_(&quot;Rp&quot;* #,##0_);_(&quot;Rp&quot;* \(#,##0\);_(&quot;Rp&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="179" formatCode="_-&quot;Rp&quot;* #,##0_-;\-&quot;Rp&quot;* #,##0_-;_-&quot;Rp&quot;* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -191,17 +191,16 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color rgb="FF3F3F3F"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -219,19 +218,18 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -242,8 +240,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -257,17 +256,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF9C6500"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -275,14 +265,54 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -295,39 +325,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF7F7F7F"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -342,13 +342,127 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -360,55 +474,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -420,109 +522,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -887,6 +887,60 @@
       </top>
       <bottom style="double">
         <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -915,69 +969,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -988,24 +979,33 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="7" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="179" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="7" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1013,131 +1013,131 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0">
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="30">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="32">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="33">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="32">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="31">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="32">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="28">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="29">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="29">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="28">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="28">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="31">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="30">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="33">
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="29">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="35">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="34">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="30">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="34">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="35">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0">
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0">
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="8" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1155,19 +1155,22 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="4" xfId="8" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="4" xfId="8" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="5" xfId="8" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="5" xfId="8" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="5" xfId="8" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="7" xfId="8" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="7" xfId="8" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="8" xfId="8" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="8" xfId="8" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="8" applyFont="1" applyBorder="1"/>
@@ -1179,17 +1182,17 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="13" xfId="8" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="13" xfId="8" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="8" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="8" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" xfId="8" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="8" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" indent="1"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="8" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="8" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="8" applyFont="1" applyAlignment="1">
@@ -1202,7 +1205,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="15" xfId="8" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="15" xfId="8" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1214,7 +1217,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="19" xfId="8" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="19" xfId="8" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="8" applyFont="1" applyBorder="1"/>
@@ -1227,7 +1230,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="8" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="8" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="8" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1596,7 +1599,7 @@
       <c r="J2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="K2" s="26"/>
+      <c r="K2" s="27"/>
       <c r="L2" s="2"/>
       <c r="M2" s="2"/>
       <c r="N2" s="2"/>
@@ -1618,7 +1621,7 @@
       <c r="J3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="K3" s="26"/>
+      <c r="K3" s="27"/>
       <c r="L3" s="2"/>
       <c r="M3" s="2"/>
       <c r="N3" s="2"/>
@@ -1664,7 +1667,7 @@
       <c r="J5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="K5" s="26"/>
+      <c r="K5" s="27"/>
       <c r="L5" s="2"/>
       <c r="M5" s="2"/>
       <c r="N5" s="2" t="s">
@@ -1712,7 +1715,7 @@
       <c r="J7" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="K7" s="26"/>
+      <c r="K7" s="27"/>
       <c r="L7" s="2"/>
       <c r="M7" s="2"/>
       <c r="N7" s="2">
@@ -1817,11 +1820,11 @@
       <c r="C11" s="8">
         <v>0</v>
       </c>
-      <c r="D11" s="8">
-        <f t="shared" ref="D11:D25" si="0">B11+C11</f>
-        <v>0</v>
-      </c>
-      <c r="E11" s="44" t="s">
+      <c r="D11" s="9">
+        <f t="shared" ref="D11:D25" si="0">IF(C11="TTU",B11,B11+C11)</f>
+        <v>0</v>
+      </c>
+      <c r="E11" s="45" t="s">
         <v>12</v>
       </c>
       <c r="F11" s="6">
@@ -1833,23 +1836,23 @@
       <c r="H11" s="8">
         <v>0</v>
       </c>
-      <c r="I11" s="8">
-        <f t="shared" ref="I11:I26" si="1">G11+H11</f>
+      <c r="I11" s="9">
+        <f t="shared" ref="I11:I26" si="1">IF(H11="TTU",G11,G11+H11)</f>
         <v>0</v>
       </c>
       <c r="J11" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="K11" s="27">
+      <c r="K11" s="28">
         <v>1</v>
       </c>
       <c r="L11" s="8">
         <v>0</v>
       </c>
-      <c r="M11" s="28" t="s">
-        <v>25</v>
-      </c>
-      <c r="N11" s="29">
+      <c r="M11" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="N11" s="30">
         <v>16</v>
       </c>
       <c r="O11" s="8">
@@ -1864,7 +1867,7 @@
       </c>
     </row>
     <row r="12" spans="1:22">
-      <c r="A12" s="9">
+      <c r="A12" s="10">
         <v>2</v>
       </c>
       <c r="B12" s="7">
@@ -1873,45 +1876,45 @@
       <c r="C12" s="8">
         <v>0</v>
       </c>
-      <c r="D12" s="8">
+      <c r="D12" s="9">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="F12" s="9">
+      <c r="F12" s="10">
         <v>17</v>
       </c>
-      <c r="G12" s="10">
+      <c r="G12" s="11">
         <v>0</v>
       </c>
       <c r="H12" s="8">
         <v>0</v>
       </c>
-      <c r="I12" s="8">
+      <c r="I12" s="9">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J12" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="K12" s="30">
+      <c r="K12" s="31">
         <v>2</v>
       </c>
       <c r="L12" s="8">
         <v>0</v>
       </c>
-      <c r="M12" s="28" t="s">
-        <v>25</v>
-      </c>
-      <c r="N12" s="31">
+      <c r="M12" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="N12" s="32">
         <v>17</v>
       </c>
       <c r="O12" s="8">
         <v>0</v>
       </c>
-      <c r="P12" s="10" t="s">
+      <c r="P12" s="11" t="s">
         <v>25</v>
       </c>
       <c r="V12">
@@ -1920,7 +1923,7 @@
       </c>
     </row>
     <row r="13" spans="1:22">
-      <c r="A13" s="9">
+      <c r="A13" s="10">
         <v>3</v>
       </c>
       <c r="B13" s="7">
@@ -1929,45 +1932,45 @@
       <c r="C13" s="8">
         <v>0</v>
       </c>
-      <c r="D13" s="8">
+      <c r="D13" s="9">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="E13" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="F13" s="9">
+      <c r="F13" s="10">
         <v>18</v>
       </c>
-      <c r="G13" s="10">
+      <c r="G13" s="11">
         <v>0</v>
       </c>
       <c r="H13" s="8">
         <v>0</v>
       </c>
-      <c r="I13" s="8">
+      <c r="I13" s="9">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J13" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="K13" s="30">
+      <c r="K13" s="31">
         <v>3</v>
       </c>
       <c r="L13" s="8">
         <v>0</v>
       </c>
-      <c r="M13" s="28" t="s">
-        <v>25</v>
-      </c>
-      <c r="N13" s="31">
+      <c r="M13" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="N13" s="32">
         <v>18</v>
       </c>
       <c r="O13" s="8">
         <v>0</v>
       </c>
-      <c r="P13" s="10" t="s">
+      <c r="P13" s="11" t="s">
         <v>25</v>
       </c>
       <c r="V13">
@@ -1976,7 +1979,7 @@
       </c>
     </row>
     <row r="14" spans="1:22">
-      <c r="A14" s="9">
+      <c r="A14" s="10">
         <v>4</v>
       </c>
       <c r="B14" s="7">
@@ -1985,55 +1988,55 @@
       <c r="C14" s="8">
         <v>0</v>
       </c>
-      <c r="D14" s="8">
+      <c r="D14" s="9">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="F14" s="9">
+      <c r="F14" s="10">
         <v>19</v>
       </c>
-      <c r="G14" s="10">
+      <c r="G14" s="11">
         <v>0</v>
       </c>
       <c r="H14" s="8">
         <v>0</v>
       </c>
-      <c r="I14" s="8">
+      <c r="I14" s="9">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J14" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="K14" s="30">
+      <c r="K14" s="31">
         <v>4</v>
       </c>
       <c r="L14" s="8">
         <v>0</v>
       </c>
-      <c r="M14" s="28" t="s">
-        <v>25</v>
-      </c>
-      <c r="N14" s="31">
+      <c r="M14" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="N14" s="32">
         <v>19</v>
       </c>
       <c r="O14" s="8">
         <v>0</v>
       </c>
-      <c r="P14" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="U14" s="43"/>
+      <c r="P14" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="U14" s="44"/>
       <c r="V14">
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
     </row>
     <row r="15" spans="1:22">
-      <c r="A15" s="9">
+      <c r="A15" s="10">
         <v>5</v>
       </c>
       <c r="B15" s="7">
@@ -2042,216 +2045,216 @@
       <c r="C15" s="8">
         <v>0</v>
       </c>
-      <c r="D15" s="8">
+      <c r="D15" s="9">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="E15" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="F15" s="9">
+      <c r="F15" s="10">
         <v>20</v>
       </c>
-      <c r="G15" s="10">
+      <c r="G15" s="11">
         <v>0</v>
       </c>
       <c r="H15" s="8">
         <v>0</v>
       </c>
-      <c r="I15" s="8">
+      <c r="I15" s="9">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J15" s="44" t="s">
-        <v>12</v>
-      </c>
-      <c r="K15" s="30">
+      <c r="J15" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="K15" s="31">
         <v>5</v>
       </c>
       <c r="L15" s="8">
         <v>0</v>
       </c>
-      <c r="M15" s="28" t="s">
-        <v>25</v>
-      </c>
-      <c r="N15" s="31">
+      <c r="M15" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="N15" s="32">
         <v>20</v>
       </c>
       <c r="O15" s="8">
         <v>0</v>
       </c>
-      <c r="P15" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="U15" s="43"/>
+      <c r="P15" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="U15" s="44"/>
       <c r="V15">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:22">
-      <c r="A16" s="9">
+      <c r="A16" s="10">
         <v>6</v>
       </c>
-      <c r="B16" s="11">
+      <c r="B16" s="12">
         <v>0</v>
       </c>
       <c r="C16" s="8">
         <v>0</v>
       </c>
-      <c r="D16" s="8">
+      <c r="D16" s="9">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="F16" s="9">
+      <c r="F16" s="10">
         <v>21</v>
       </c>
-      <c r="G16" s="10">
+      <c r="G16" s="11">
         <v>0</v>
       </c>
       <c r="H16" s="8">
         <v>0</v>
       </c>
-      <c r="I16" s="8">
+      <c r="I16" s="9">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J16" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="K16" s="30">
+      <c r="K16" s="31">
         <v>6</v>
       </c>
       <c r="L16" s="8">
         <v>0</v>
       </c>
-      <c r="M16" s="28" t="s">
-        <v>25</v>
-      </c>
-      <c r="N16" s="31">
+      <c r="M16" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="N16" s="32">
         <v>21</v>
       </c>
       <c r="O16" s="8">
         <v>0</v>
       </c>
-      <c r="P16" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="U16" s="43"/>
+      <c r="P16" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="U16" s="44"/>
       <c r="V16">
         <f t="shared" si="2"/>
         <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:22">
-      <c r="A17" s="9">
+      <c r="A17" s="10">
         <v>7</v>
       </c>
-      <c r="B17" s="11">
+      <c r="B17" s="12">
         <v>0</v>
       </c>
       <c r="C17" s="8">
         <v>0</v>
       </c>
-      <c r="D17" s="8">
+      <c r="D17" s="9">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="E17" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="F17" s="9">
+      <c r="F17" s="10">
         <v>22</v>
       </c>
-      <c r="G17" s="10">
+      <c r="G17" s="11">
         <v>0</v>
       </c>
       <c r="H17" s="8">
         <v>0</v>
       </c>
-      <c r="I17" s="8">
+      <c r="I17" s="9">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J17" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="K17" s="30">
+      <c r="K17" s="31">
         <v>7</v>
       </c>
       <c r="L17" s="8">
         <v>0</v>
       </c>
-      <c r="M17" s="28" t="s">
-        <v>25</v>
-      </c>
-      <c r="N17" s="31">
+      <c r="M17" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="N17" s="32">
         <v>22</v>
       </c>
       <c r="O17" s="8">
         <v>0</v>
       </c>
-      <c r="P17" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="U17" s="43"/>
+      <c r="P17" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="U17" s="44"/>
       <c r="V17">
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
     </row>
     <row r="18" spans="1:22">
-      <c r="A18" s="9">
+      <c r="A18" s="10">
         <v>8</v>
       </c>
-      <c r="B18" s="11">
+      <c r="B18" s="12">
         <v>0</v>
       </c>
       <c r="C18" s="8">
         <v>0</v>
       </c>
-      <c r="D18" s="8">
+      <c r="D18" s="9">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="F18" s="9">
+      <c r="F18" s="10">
         <v>23</v>
       </c>
-      <c r="G18" s="10">
+      <c r="G18" s="11">
         <v>0</v>
       </c>
       <c r="H18" s="8">
         <v>0</v>
       </c>
-      <c r="I18" s="8">
+      <c r="I18" s="9">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J18" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="K18" s="30">
+      <c r="K18" s="31">
         <v>8</v>
       </c>
       <c r="L18" s="8">
         <v>0</v>
       </c>
-      <c r="M18" s="28" t="s">
-        <v>25</v>
-      </c>
-      <c r="N18" s="31">
+      <c r="M18" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="N18" s="32">
         <v>23</v>
       </c>
       <c r="O18" s="8">
         <v>0</v>
       </c>
-      <c r="P18" s="10" t="s">
+      <c r="P18" s="11" t="s">
         <v>25</v>
       </c>
       <c r="V18">
@@ -2260,54 +2263,54 @@
       </c>
     </row>
     <row r="19" spans="1:22">
-      <c r="A19" s="9">
+      <c r="A19" s="10">
         <v>9</v>
       </c>
-      <c r="B19" s="11">
+      <c r="B19" s="12">
         <v>0</v>
       </c>
       <c r="C19" s="8">
         <v>0</v>
       </c>
-      <c r="D19" s="8">
+      <c r="D19" s="9">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="E19" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="F19" s="9">
+      <c r="F19" s="10">
         <v>24</v>
       </c>
-      <c r="G19" s="10">
+      <c r="G19" s="11">
         <v>0</v>
       </c>
       <c r="H19" s="8">
         <v>0</v>
       </c>
-      <c r="I19" s="8">
+      <c r="I19" s="9">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J19" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="K19" s="30">
+      <c r="K19" s="31">
         <v>9</v>
       </c>
       <c r="L19" s="8">
         <v>0</v>
       </c>
-      <c r="M19" s="28" t="s">
-        <v>25</v>
-      </c>
-      <c r="N19" s="31">
+      <c r="M19" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="N19" s="32">
         <v>24</v>
       </c>
       <c r="O19" s="8">
         <v>0</v>
       </c>
-      <c r="P19" s="10" t="s">
+      <c r="P19" s="11" t="s">
         <v>25</v>
       </c>
       <c r="V19">
@@ -2316,54 +2319,54 @@
       </c>
     </row>
     <row r="20" spans="1:22">
-      <c r="A20" s="9">
+      <c r="A20" s="10">
         <v>10</v>
       </c>
-      <c r="B20" s="11">
+      <c r="B20" s="12">
         <v>0</v>
       </c>
       <c r="C20" s="8">
         <v>0</v>
       </c>
-      <c r="D20" s="8">
+      <c r="D20" s="9">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="F20" s="9">
-        <v>25</v>
-      </c>
-      <c r="G20" s="10">
+      <c r="F20" s="10">
+        <v>25</v>
+      </c>
+      <c r="G20" s="11">
         <v>0</v>
       </c>
       <c r="H20" s="8">
         <v>0</v>
       </c>
-      <c r="I20" s="8">
+      <c r="I20" s="9">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J20" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="K20" s="30">
+      <c r="K20" s="31">
         <v>10</v>
       </c>
       <c r="L20" s="8">
         <v>0</v>
       </c>
-      <c r="M20" s="28" t="s">
-        <v>25</v>
-      </c>
-      <c r="N20" s="31">
+      <c r="M20" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="N20" s="32">
         <v>25</v>
       </c>
       <c r="O20" s="8">
         <v>0</v>
       </c>
-      <c r="P20" s="10" t="s">
+      <c r="P20" s="11" t="s">
         <v>25</v>
       </c>
       <c r="V20">
@@ -2372,54 +2375,54 @@
       </c>
     </row>
     <row r="21" spans="1:22">
-      <c r="A21" s="9">
+      <c r="A21" s="10">
         <v>11</v>
       </c>
-      <c r="B21" s="11">
+      <c r="B21" s="12">
         <v>0</v>
       </c>
       <c r="C21" s="8">
         <v>0</v>
       </c>
-      <c r="D21" s="8">
+      <c r="D21" s="9">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="E21" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="F21" s="9">
+      <c r="F21" s="10">
         <v>26</v>
       </c>
-      <c r="G21" s="10">
+      <c r="G21" s="11">
         <v>0</v>
       </c>
       <c r="H21" s="8">
         <v>0</v>
       </c>
-      <c r="I21" s="8">
+      <c r="I21" s="9">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J21" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="K21" s="30">
+      <c r="K21" s="31">
         <v>11</v>
       </c>
       <c r="L21" s="8">
         <v>0</v>
       </c>
-      <c r="M21" s="28" t="s">
-        <v>25</v>
-      </c>
-      <c r="N21" s="31">
+      <c r="M21" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="N21" s="32">
         <v>26</v>
       </c>
       <c r="O21" s="8">
         <v>0</v>
       </c>
-      <c r="P21" s="10" t="s">
+      <c r="P21" s="11" t="s">
         <v>25</v>
       </c>
       <c r="V21">
@@ -2428,54 +2431,54 @@
       </c>
     </row>
     <row r="22" spans="1:22">
-      <c r="A22" s="9">
-        <v>12</v>
-      </c>
-      <c r="B22" s="11">
+      <c r="A22" s="10">
+        <v>12</v>
+      </c>
+      <c r="B22" s="12">
         <v>0</v>
       </c>
       <c r="C22" s="8">
         <v>0</v>
       </c>
-      <c r="D22" s="8">
+      <c r="D22" s="9">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="F22" s="9">
+      <c r="F22" s="10">
         <v>27</v>
       </c>
-      <c r="G22" s="10">
+      <c r="G22" s="11">
         <v>0</v>
       </c>
       <c r="H22" s="8">
         <v>0</v>
       </c>
-      <c r="I22" s="8">
-        <f t="shared" si="1"/>
+      <c r="I22" s="9">
+        <f>IF(H22="TTU",G22,G22+H22)</f>
         <v>0</v>
       </c>
       <c r="J22" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="K22" s="30">
+      <c r="K22" s="31">
         <v>12</v>
       </c>
       <c r="L22" s="8">
         <v>0</v>
       </c>
-      <c r="M22" s="28" t="s">
-        <v>25</v>
-      </c>
-      <c r="N22" s="31">
+      <c r="M22" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="N22" s="32">
         <v>27</v>
       </c>
       <c r="O22" s="8">
         <v>0</v>
       </c>
-      <c r="P22" s="10" t="s">
+      <c r="P22" s="11" t="s">
         <v>25</v>
       </c>
       <c r="V22">
@@ -2484,54 +2487,54 @@
       </c>
     </row>
     <row r="23" spans="1:22">
-      <c r="A23" s="9">
+      <c r="A23" s="10">
         <v>13</v>
       </c>
-      <c r="B23" s="11">
+      <c r="B23" s="12">
         <v>0</v>
       </c>
       <c r="C23" s="8">
         <v>0</v>
       </c>
-      <c r="D23" s="8">
+      <c r="D23" s="9">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="E23" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="F23" s="9">
+      <c r="F23" s="10">
         <v>28</v>
       </c>
-      <c r="G23" s="10">
+      <c r="G23" s="11">
         <v>0</v>
       </c>
       <c r="H23" s="8">
         <v>0</v>
       </c>
-      <c r="I23" s="8">
+      <c r="I23" s="9">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J23" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="K23" s="30">
+      <c r="K23" s="31">
         <v>13</v>
       </c>
       <c r="L23" s="8">
         <v>0</v>
       </c>
-      <c r="M23" s="28" t="s">
-        <v>25</v>
-      </c>
-      <c r="N23" s="31">
+      <c r="M23" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="N23" s="32">
         <v>28</v>
       </c>
       <c r="O23" s="8">
         <v>0</v>
       </c>
-      <c r="P23" s="32" t="s">
+      <c r="P23" s="33" t="s">
         <v>25</v>
       </c>
       <c r="V23">
@@ -2540,54 +2543,54 @@
       </c>
     </row>
     <row r="24" spans="1:22">
-      <c r="A24" s="9">
+      <c r="A24" s="10">
         <v>14</v>
       </c>
-      <c r="B24" s="11">
+      <c r="B24" s="12">
         <v>0</v>
       </c>
       <c r="C24" s="8">
         <v>0</v>
       </c>
-      <c r="D24" s="8">
+      <c r="D24" s="9">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="F24" s="9">
+      <c r="F24" s="10">
         <v>29</v>
       </c>
-      <c r="G24" s="10">
+      <c r="G24" s="11">
         <v>0</v>
       </c>
       <c r="H24" s="8">
         <v>0</v>
       </c>
-      <c r="I24" s="8">
+      <c r="I24" s="9">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J24" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="K24" s="30">
+      <c r="K24" s="31">
         <v>14</v>
       </c>
       <c r="L24" s="8">
         <v>0</v>
       </c>
-      <c r="M24" s="28" t="s">
-        <v>25</v>
-      </c>
-      <c r="N24" s="31">
+      <c r="M24" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="N24" s="32">
         <v>29</v>
       </c>
       <c r="O24" s="8">
         <v>0</v>
       </c>
-      <c r="P24" s="10" t="s">
+      <c r="P24" s="11" t="s">
         <v>25</v>
       </c>
       <c r="V24">
@@ -2596,54 +2599,54 @@
       </c>
     </row>
     <row r="25" spans="1:22">
-      <c r="A25" s="9">
+      <c r="A25" s="10">
         <v>15</v>
       </c>
-      <c r="B25" s="11">
+      <c r="B25" s="12">
         <v>0</v>
       </c>
       <c r="C25" s="8">
         <v>0</v>
       </c>
-      <c r="D25" s="8">
+      <c r="D25" s="9">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E25" s="44" t="s">
-        <v>12</v>
-      </c>
-      <c r="F25" s="9">
+      <c r="E25" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="F25" s="10">
         <v>30</v>
       </c>
-      <c r="G25" s="10">
+      <c r="G25" s="11">
         <v>0</v>
       </c>
       <c r="H25" s="8">
         <v>0</v>
       </c>
-      <c r="I25" s="8">
+      <c r="I25" s="9">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J25" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="K25" s="30">
+      <c r="K25" s="31">
         <v>15</v>
       </c>
       <c r="L25" s="8">
         <v>0</v>
       </c>
-      <c r="M25" s="28" t="s">
-        <v>25</v>
-      </c>
-      <c r="N25" s="31">
+      <c r="M25" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="N25" s="32">
         <v>30</v>
       </c>
       <c r="O25" s="8">
         <v>0</v>
       </c>
-      <c r="P25" s="10" t="s">
+      <c r="P25" s="11" t="s">
         <v>25</v>
       </c>
       <c r="V25">
@@ -2652,37 +2655,37 @@
       </c>
     </row>
     <row r="26" spans="1:22">
-      <c r="A26" s="12"/>
-      <c r="B26" s="13"/>
-      <c r="C26" s="14"/>
+      <c r="A26" s="13"/>
+      <c r="B26" s="14"/>
+      <c r="C26" s="15"/>
       <c r="D26" s="8"/>
-      <c r="E26" s="12"/>
-      <c r="F26" s="9">
+      <c r="E26" s="13"/>
+      <c r="F26" s="10">
         <v>31</v>
       </c>
-      <c r="G26" s="10">
+      <c r="G26" s="11">
         <v>0</v>
       </c>
       <c r="H26" s="8">
         <v>0</v>
       </c>
-      <c r="I26" s="8">
+      <c r="I26" s="9">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J26" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="K26" s="33"/>
-      <c r="L26" s="13"/>
-      <c r="M26" s="34"/>
-      <c r="N26" s="31">
+      <c r="K26" s="34"/>
+      <c r="L26" s="14"/>
+      <c r="M26" s="35"/>
+      <c r="N26" s="32">
         <v>31</v>
       </c>
       <c r="O26" s="8">
         <v>0</v>
       </c>
-      <c r="P26" s="10" t="s">
+      <c r="P26" s="11" t="s">
         <v>25</v>
       </c>
       <c r="V26">
@@ -2691,66 +2694,66 @@
       </c>
     </row>
     <row r="27" ht="13.5" customHeight="1" spans="1:22">
-      <c r="A27" s="15"/>
-      <c r="B27" s="16"/>
-      <c r="C27" s="17"/>
-      <c r="D27" s="17"/>
-      <c r="E27" s="15"/>
-      <c r="F27" s="15"/>
-      <c r="G27" s="17"/>
-      <c r="H27" s="17"/>
-      <c r="I27" s="17"/>
-      <c r="J27" s="15"/>
-      <c r="K27" s="35"/>
-      <c r="L27" s="16"/>
-      <c r="M27" s="36"/>
-      <c r="N27" s="37"/>
-      <c r="O27" s="16"/>
-      <c r="P27" s="17"/>
+      <c r="A27" s="16"/>
+      <c r="B27" s="17"/>
+      <c r="C27" s="18"/>
+      <c r="D27" s="18"/>
+      <c r="E27" s="16"/>
+      <c r="F27" s="16"/>
+      <c r="G27" s="18"/>
+      <c r="H27" s="18"/>
+      <c r="I27" s="18"/>
+      <c r="J27" s="16"/>
+      <c r="K27" s="36"/>
+      <c r="L27" s="17"/>
+      <c r="M27" s="37"/>
+      <c r="N27" s="38"/>
+      <c r="O27" s="17"/>
+      <c r="P27" s="18"/>
       <c r="V27">
         <f t="shared" si="3"/>
         <v>17</v>
       </c>
     </row>
     <row r="28" ht="13.5" spans="1:22">
-      <c r="A28" s="18" t="s">
+      <c r="A28" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="B28" s="19">
+      <c r="B28" s="20">
         <f>SUM(B11:B25)</f>
         <v>0</v>
       </c>
-      <c r="C28" s="19">
+      <c r="C28" s="20">
         <f>SUM(C11:C25)</f>
         <v>0</v>
       </c>
-      <c r="D28" s="19">
+      <c r="D28" s="20">
         <f>SUM(D11:D25)</f>
         <v>0</v>
       </c>
-      <c r="E28" s="20"/>
-      <c r="F28" s="18" t="s">
+      <c r="E28" s="21"/>
+      <c r="F28" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="G28" s="19">
+      <c r="G28" s="20">
         <f>SUM(G11:G26)</f>
         <v>0</v>
       </c>
-      <c r="H28" s="19">
+      <c r="H28" s="20">
         <f>SUM(H11:H26)</f>
         <v>0</v>
       </c>
-      <c r="I28" s="19">
+      <c r="I28" s="20">
         <f>SUM(I11:I26)</f>
         <v>0</v>
       </c>
-      <c r="J28" s="20"/>
-      <c r="K28" s="38"/>
-      <c r="L28" s="39"/>
-      <c r="M28" s="40"/>
-      <c r="N28" s="41"/>
-      <c r="O28" s="39"/>
-      <c r="P28" s="42"/>
+      <c r="J28" s="21"/>
+      <c r="K28" s="39"/>
+      <c r="L28" s="40"/>
+      <c r="M28" s="41"/>
+      <c r="N28" s="42"/>
+      <c r="O28" s="40"/>
+      <c r="P28" s="43"/>
       <c r="V28">
         <f t="shared" si="3"/>
         <v>18</v>
@@ -2781,9 +2784,9 @@
       <c r="A31" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B31" s="21"/>
-      <c r="C31" s="22"/>
-      <c r="D31" s="23">
+      <c r="B31" s="22"/>
+      <c r="C31" s="23"/>
+      <c r="D31" s="24">
         <f>C28+H28</f>
         <v>0</v>
       </c>
@@ -2798,8 +2801,8 @@
         <v>30</v>
       </c>
       <c r="B32" s="2"/>
-      <c r="C32" s="24"/>
-      <c r="D32" s="23">
+      <c r="C32" s="25"/>
+      <c r="D32" s="24">
         <f>D28+I28</f>
         <v>0</v>
       </c>
@@ -2829,8 +2832,8 @@
         <v>33</v>
       </c>
       <c r="B33" s="2"/>
-      <c r="C33" s="22"/>
-      <c r="D33" s="25">
+      <c r="C33" s="23"/>
+      <c r="D33" s="26">
         <f>COUNTIF(C11:C25,"&gt;0")+COUNTIF(C11:C25,"TTU")+COUNTIF(H11:H26,"&gt;0")+COUNTIF(H11:H26,"TTU")</f>
         <v>0</v>
       </c>
@@ -2859,7 +2862,7 @@
       <c r="A34" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="D34" s="25">
+      <c r="D34" s="26">
         <f>V41</f>
         <v>31</v>
       </c>
@@ -2887,7 +2890,7 @@
       <c r="A35" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="D35" s="25">
+      <c r="D35" s="26">
         <f>MAX(V11:V41)</f>
         <v>31</v>
       </c>
@@ -2898,7 +2901,7 @@
       <c r="H35" s="2"/>
       <c r="I35" s="2"/>
       <c r="J35" s="2"/>
-      <c r="K35" s="45" t="s">
+      <c r="K35" s="46" t="s">
         <v>41</v>
       </c>
       <c r="L35" s="2"/>

--- a/TEMPLATE PENGUAPAN.xlsx
+++ b/TEMPLATE PENGUAPAN.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24332"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zavie\Downloads\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41B26B0C-91BD-42FA-825D-B222DCD9888E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="28125" windowHeight="12495"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Penguapan" sheetId="1" r:id="rId1"/>
@@ -13,13 +19,14 @@
     <definedName name="_LPM2">#REF!</definedName>
     <definedName name="_LPM3">#REF!</definedName>
     <definedName name="NONA">#REF!</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Penguapan!$A$1:$P$35</definedName>
   </definedNames>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="48">
   <si>
     <t>HTH helper: &lt;1 mm = tanpa hujan; &gt;=1 mm/TTU = hujan</t>
   </si>
@@ -33,15 +40,9 @@
     <t>:  2026</t>
   </si>
   <si>
-    <t>STASIUN PENGUAPAN NO.    :  049</t>
-  </si>
-  <si>
     <t>BULAN</t>
   </si>
   <si>
-    <t>STASIUN HUJAN NO.              :  461</t>
-  </si>
-  <si>
     <t>TEMPAT PEMERIKSAAN</t>
   </si>
   <si>
@@ -54,9 +55,6 @@
     <t>:  Kambera</t>
   </si>
   <si>
-    <t>PEMERIKSAAN PENGUAPAN TIAP PAGI JAM :</t>
-  </si>
-  <si>
     <t>08.00</t>
   </si>
   <si>
@@ -72,9 +70,6 @@
     <t>:  Nusa Tenggara Timur</t>
   </si>
   <si>
-    <t>JIKA TAK ADA HUJAN KOLOM HUJAN DIISI  :</t>
-  </si>
-  <si>
     <t>Tanggal Pengukuran</t>
   </si>
   <si>
@@ -145,20 +140,46 @@
   </si>
   <si>
     <t>//// = Air dalam panci penguapan meluap karena hujan sedang - lebat</t>
+  </si>
+  <si>
+    <t>:  049</t>
+  </si>
+  <si>
+    <t>STASIUN PENGUAPAN NO.</t>
+  </si>
+  <si>
+    <t>STASIUN HUJAN NO.</t>
+  </si>
+  <si>
+    <t>:  461</t>
+  </si>
+  <si>
+    <t>: 08.00</t>
+  </si>
+  <si>
+    <t>PEMERIKSAAN PENGUAPAN</t>
+  </si>
+  <si>
+    <t>TIAP PAGI JAM</t>
+  </si>
+  <si>
+    <t>JIKA TAK ADA HUJAN</t>
+  </si>
+  <si>
+    <t>KOLOM HUJAN DIISI  :</t>
+  </si>
+  <si>
+    <t>: 0</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_(&quot;Rp&quot;* #,##0_);_(&quot;Rp&quot;* \(#,##0\);_(&quot;Rp&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="177" formatCode="0.0"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;Rp&quot;* #,##0_-;\-&quot;Rp&quot;* #,##0_-;_-&quot;Rp&quot;* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_-&quot;Rp&quot;* #,##0.00_-;\-&quot;Rp&quot;* #,##0.00_-;_-&quot;Rp&quot;* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="166" formatCode="0.0"/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="6">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -182,352 +203,25 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <charset val="134"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <sz val="8"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="36">
+  <borders count="28">
     <border>
       <left/>
       <right/>
@@ -890,410 +584,136 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="50">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="7" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="7" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="7" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="30">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="32">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="33">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="32">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="31">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="29">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="28">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="29">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="35">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="34">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="8" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="8" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="8" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="4" xfId="8" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="5" xfId="8" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="5" xfId="8" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="7" xfId="8" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="8" xfId="8" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="8" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="8" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="8" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="8" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="8" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="8" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" indent="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="13" xfId="8" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="8" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" xfId="8" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="8" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" indent="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="8" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="8" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="8" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="8"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="15" xfId="8" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="19" xfId="8" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="8" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="8" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="8" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="8" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="8" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="8" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="8" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="8" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="8" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="8" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="8" applyFont="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="left" indent="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="50">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="40% - Accent1" xfId="1" builtinId="31"/>
-    <cellStyle name="Comma" xfId="2" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="3" builtinId="6"/>
-    <cellStyle name="Currency [0]" xfId="4" builtinId="7"/>
-    <cellStyle name="Currency" xfId="5" builtinId="4"/>
-    <cellStyle name="Percent" xfId="6" builtinId="5"/>
-    <cellStyle name="Hyperlink" xfId="7" builtinId="8"/>
-    <cellStyle name="Normal_Sheet1" xfId="8"/>
-    <cellStyle name="60% - Accent4" xfId="9" builtinId="44"/>
-    <cellStyle name="Followed Hyperlink" xfId="10" builtinId="9"/>
-    <cellStyle name="Check Cell" xfId="11" builtinId="23"/>
-    <cellStyle name="Heading 2" xfId="12" builtinId="17"/>
-    <cellStyle name="Note" xfId="13" builtinId="10"/>
-    <cellStyle name="40% - Accent3" xfId="14" builtinId="39"/>
-    <cellStyle name="Warning Text" xfId="15" builtinId="11"/>
-    <cellStyle name="40% - Accent2" xfId="16" builtinId="35"/>
-    <cellStyle name="Title" xfId="17" builtinId="15"/>
-    <cellStyle name="CExplanatory Text" xfId="18" builtinId="53"/>
-    <cellStyle name="Heading 1" xfId="19" builtinId="16"/>
-    <cellStyle name="Heading 3" xfId="20" builtinId="18"/>
-    <cellStyle name="Heading 4" xfId="21" builtinId="19"/>
-    <cellStyle name="Input" xfId="22" builtinId="20"/>
-    <cellStyle name="60% - Accent3" xfId="23" builtinId="40"/>
-    <cellStyle name="Good" xfId="24" builtinId="26"/>
-    <cellStyle name="Output" xfId="25" builtinId="21"/>
-    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
-    <cellStyle name="Calculation" xfId="27" builtinId="22"/>
-    <cellStyle name="Linked Cell" xfId="28" builtinId="24"/>
-    <cellStyle name="Total" xfId="29" builtinId="25"/>
-    <cellStyle name="Bad" xfId="30" builtinId="27"/>
-    <cellStyle name="Neutral" xfId="31" builtinId="28"/>
-    <cellStyle name="Accent1" xfId="32" builtinId="29"/>
-    <cellStyle name="20% - Accent5" xfId="33" builtinId="46"/>
-    <cellStyle name="60% - Accent1" xfId="34" builtinId="32"/>
-    <cellStyle name="Accent2" xfId="35" builtinId="33"/>
-    <cellStyle name="20% - Accent2" xfId="36" builtinId="34"/>
-    <cellStyle name="20% - Accent6" xfId="37" builtinId="50"/>
-    <cellStyle name="60% - Accent2" xfId="38" builtinId="36"/>
-    <cellStyle name="Accent3" xfId="39" builtinId="37"/>
-    <cellStyle name="20% - Accent3" xfId="40" builtinId="38"/>
-    <cellStyle name="Accent4" xfId="41" builtinId="41"/>
-    <cellStyle name="20% - Accent4" xfId="42" builtinId="42"/>
-    <cellStyle name="40% - Accent4" xfId="43" builtinId="43"/>
-    <cellStyle name="Accent5" xfId="44" builtinId="45"/>
-    <cellStyle name="40% - Accent5" xfId="45" builtinId="47"/>
-    <cellStyle name="60% - Accent5" xfId="46" builtinId="48"/>
-    <cellStyle name="Accent6" xfId="47" builtinId="49"/>
-    <cellStyle name="40% - Accent6" xfId="48" builtinId="51"/>
-    <cellStyle name="60% - Accent6" xfId="49" builtinId="52"/>
+    <cellStyle name="Normal_Sheet1" xfId="1" xr:uid="{00000000-0005-0000-0000-000008000000}"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1551,36 +971,37 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:V41"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="11.2857142857143" customWidth="1"/>
-    <col min="4" max="4" width="10.5714285714286" customWidth="1"/>
-    <col min="5" max="5" width="5.85714285714286" customWidth="1"/>
-    <col min="6" max="6" width="11.4285714285714" customWidth="1"/>
-    <col min="9" max="9" width="10.5714285714286" customWidth="1"/>
-    <col min="10" max="10" width="6.42857142857143" customWidth="1"/>
-    <col min="11" max="11" width="11.4285714285714" customWidth="1"/>
-    <col min="12" max="12" width="7.85714285714286" customWidth="1"/>
-    <col min="15" max="15" width="7.85714285714286" customWidth="1"/>
-    <col min="19" max="19" width="12.8571428571429" customWidth="1"/>
+    <col min="1" max="1" width="11.28515625" customWidth="1"/>
+    <col min="4" max="4" width="10.5703125" customWidth="1"/>
+    <col min="5" max="5" width="5.85546875" customWidth="1"/>
+    <col min="6" max="6" width="11.42578125" customWidth="1"/>
+    <col min="9" max="9" width="10.5703125" customWidth="1"/>
+    <col min="10" max="10" width="6.42578125" customWidth="1"/>
+    <col min="11" max="11" width="11.42578125" customWidth="1"/>
+    <col min="12" max="12" width="7.85546875" customWidth="1"/>
+    <col min="15" max="15" width="7.85546875" customWidth="1"/>
+    <col min="19" max="19" width="12.85546875" customWidth="1"/>
     <col min="22" max="22" width="53" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="22:22">
+    <row r="1" spans="1:22">
       <c r="V1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:16">
+    <row r="2" spans="1:22">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -1596,135 +1017,141 @@
       </c>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
-      <c r="J2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="K2" s="27"/>
+      <c r="J2" s="46" t="s">
+        <v>39</v>
+      </c>
+      <c r="K2" s="2"/>
       <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
+      <c r="M2" s="47" t="s">
+        <v>38</v>
+      </c>
       <c r="N2" s="2"/>
       <c r="O2" s="2"/>
       <c r="P2" s="2"/>
     </row>
-    <row r="3" spans="1:16">
+    <row r="3" spans="1:22">
       <c r="A3" s="3"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
       <c r="E3" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
-      <c r="J3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="K3" s="27"/>
+      <c r="J3" s="46" t="s">
+        <v>40</v>
+      </c>
+      <c r="K3" s="2"/>
       <c r="L3" s="2"/>
-      <c r="M3" s="2"/>
+      <c r="M3" s="47" t="s">
+        <v>41</v>
+      </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
       <c r="P3" s="2"/>
     </row>
-    <row r="4" spans="1:16">
+    <row r="4" spans="1:22">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
       <c r="E4" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F4" s="2"/>
       <c r="G4" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
       <c r="L4" s="2"/>
-      <c r="M4" s="2"/>
+      <c r="M4" s="1"/>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
       <c r="P4" s="2"/>
     </row>
-    <row r="5" spans="1:16">
+    <row r="5" spans="1:22" ht="12.75" customHeight="1">
       <c r="A5" s="3"/>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
       <c r="E5" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
-      <c r="J5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="K5" s="27"/>
-      <c r="L5" s="2"/>
-      <c r="M5" s="2"/>
-      <c r="N5" s="2" t="s">
-        <v>12</v>
-      </c>
+      <c r="J5" s="50" t="s">
+        <v>43</v>
+      </c>
+      <c r="K5" s="49"/>
+      <c r="L5" s="49"/>
+      <c r="M5" s="48" t="s">
+        <v>42</v>
+      </c>
+      <c r="N5" s="47"/>
       <c r="O5" s="2"/>
       <c r="P5" s="2"/>
     </row>
-    <row r="6" spans="1:16">
+    <row r="6" spans="1:22">
       <c r="A6" s="3"/>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
       <c r="D6" s="3"/>
       <c r="E6" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F6" s="2"/>
       <c r="G6" s="2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
-      <c r="K6" s="2"/>
-      <c r="L6" s="2"/>
-      <c r="M6" s="2"/>
-      <c r="N6" s="2"/>
+      <c r="J6" s="50" t="s">
+        <v>44</v>
+      </c>
+      <c r="K6" s="49"/>
+      <c r="L6" s="49"/>
+      <c r="M6" s="48"/>
+      <c r="N6" s="47"/>
       <c r="O6" s="2"/>
       <c r="P6" s="2"/>
     </row>
-    <row r="7" spans="1:16">
+    <row r="7" spans="1:22">
       <c r="A7" s="3"/>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
       <c r="E7" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F7" s="2"/>
       <c r="G7" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
-      <c r="J7" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K7" s="27"/>
+      <c r="J7" s="50" t="s">
+        <v>45</v>
+      </c>
+      <c r="K7" s="26"/>
       <c r="L7" s="2"/>
-      <c r="M7" s="2"/>
-      <c r="N7" s="2">
-        <v>0</v>
-      </c>
+      <c r="M7" s="48" t="s">
+        <v>47</v>
+      </c>
+      <c r="N7" s="47"/>
       <c r="O7" s="2"/>
       <c r="P7" s="2"/>
     </row>
-    <row r="8" spans="1:16">
+    <row r="8" spans="1:22">
       <c r="A8" s="3"/>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -1734,15 +1161,17 @@
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
       <c r="I8" s="3"/>
-      <c r="J8" s="3"/>
+      <c r="J8" s="50" t="s">
+        <v>46</v>
+      </c>
       <c r="K8" s="3"/>
       <c r="L8" s="3"/>
-      <c r="M8" s="3"/>
+      <c r="M8" s="48"/>
       <c r="N8" s="3"/>
       <c r="O8" s="3"/>
       <c r="P8" s="3"/>
     </row>
-    <row r="9" ht="13.5" customHeight="1" spans="1:16">
+    <row r="9" spans="1:22" ht="13.5" customHeight="1">
       <c r="A9" s="3"/>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
@@ -1760,54 +1189,54 @@
       <c r="O9" s="3"/>
       <c r="P9" s="3"/>
     </row>
-    <row r="10" ht="35.25" customHeight="1" spans="1:16">
+    <row r="10" spans="1:22" ht="35.25" customHeight="1">
       <c r="A10" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E10" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="F10" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I10" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J10" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="K10" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="L10" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="M10" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D10" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="G10" s="4" t="s">
+      <c r="N10" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="O10" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="H10" s="4" t="s">
+      <c r="P10" s="4" t="s">
         <v>20</v>
-      </c>
-      <c r="I10" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J10" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="K10" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="L10" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="M10" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="N10" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="O10" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="P10" s="4" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -1820,12 +1249,12 @@
       <c r="C11" s="8">
         <v>0</v>
       </c>
-      <c r="D11" s="9">
+      <c r="D11" s="8">
         <f t="shared" ref="D11:D25" si="0">IF(C11="TTU",B11,B11+C11)</f>
         <v>0</v>
       </c>
-      <c r="E11" s="45" t="s">
-        <v>12</v>
+      <c r="E11" s="44" t="s">
+        <v>9</v>
       </c>
       <c r="F11" s="6">
         <v>16</v>
@@ -1836,30 +1265,30 @@
       <c r="H11" s="8">
         <v>0</v>
       </c>
-      <c r="I11" s="9">
+      <c r="I11" s="8">
         <f t="shared" ref="I11:I26" si="1">IF(H11="TTU",G11,G11+H11)</f>
         <v>0</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="K11" s="28">
+        <v>9</v>
+      </c>
+      <c r="K11" s="27">
         <v>1</v>
       </c>
       <c r="L11" s="8">
         <v>0</v>
       </c>
-      <c r="M11" s="29" t="s">
-        <v>25</v>
-      </c>
-      <c r="N11" s="30">
+      <c r="M11" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="N11" s="29">
         <v>16</v>
       </c>
       <c r="O11" s="8">
         <v>0</v>
       </c>
       <c r="P11" s="8" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="V11">
         <f>IF(OR(C11&gt;=1,C11="TTU"),0,1)</f>
@@ -1867,7 +1296,7 @@
       </c>
     </row>
     <row r="12" spans="1:22">
-      <c r="A12" s="10">
+      <c r="A12" s="9">
         <v>2</v>
       </c>
       <c r="B12" s="7">
@@ -1876,46 +1305,46 @@
       <c r="C12" s="8">
         <v>0</v>
       </c>
-      <c r="D12" s="9">
+      <c r="D12" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F12" s="10">
+        <v>9</v>
+      </c>
+      <c r="F12" s="9">
         <v>17</v>
       </c>
-      <c r="G12" s="11">
+      <c r="G12" s="10">
         <v>0</v>
       </c>
       <c r="H12" s="8">
         <v>0</v>
       </c>
-      <c r="I12" s="9">
+      <c r="I12" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="K12" s="31">
+        <v>9</v>
+      </c>
+      <c r="K12" s="30">
         <v>2</v>
       </c>
       <c r="L12" s="8">
         <v>0</v>
       </c>
-      <c r="M12" s="29" t="s">
-        <v>25</v>
-      </c>
-      <c r="N12" s="32">
+      <c r="M12" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="N12" s="31">
         <v>17</v>
       </c>
       <c r="O12" s="8">
         <v>0</v>
       </c>
-      <c r="P12" s="11" t="s">
-        <v>25</v>
+      <c r="P12" s="10" t="s">
+        <v>21</v>
       </c>
       <c r="V12">
         <f t="shared" ref="V12:V25" si="2">IF(OR(C12&gt;=1,C12="TTU"),0,V11+1)</f>
@@ -1923,7 +1352,7 @@
       </c>
     </row>
     <row r="13" spans="1:22">
-      <c r="A13" s="10">
+      <c r="A13" s="9">
         <v>3</v>
       </c>
       <c r="B13" s="7">
@@ -1932,46 +1361,46 @@
       <c r="C13" s="8">
         <v>0</v>
       </c>
-      <c r="D13" s="9">
+      <c r="D13" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F13" s="10">
+        <v>9</v>
+      </c>
+      <c r="F13" s="9">
         <v>18</v>
       </c>
-      <c r="G13" s="11">
+      <c r="G13" s="10">
         <v>0</v>
       </c>
       <c r="H13" s="8">
         <v>0</v>
       </c>
-      <c r="I13" s="9">
+      <c r="I13" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="K13" s="31">
+        <v>9</v>
+      </c>
+      <c r="K13" s="30">
         <v>3</v>
       </c>
       <c r="L13" s="8">
         <v>0</v>
       </c>
-      <c r="M13" s="29" t="s">
-        <v>25</v>
-      </c>
-      <c r="N13" s="32">
+      <c r="M13" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="N13" s="31">
         <v>18</v>
       </c>
       <c r="O13" s="8">
         <v>0</v>
       </c>
-      <c r="P13" s="11" t="s">
-        <v>25</v>
+      <c r="P13" s="10" t="s">
+        <v>21</v>
       </c>
       <c r="V13">
         <f t="shared" si="2"/>
@@ -1979,7 +1408,7 @@
       </c>
     </row>
     <row r="14" spans="1:22">
-      <c r="A14" s="10">
+      <c r="A14" s="9">
         <v>4</v>
       </c>
       <c r="B14" s="7">
@@ -1988,55 +1417,55 @@
       <c r="C14" s="8">
         <v>0</v>
       </c>
-      <c r="D14" s="9">
+      <c r="D14" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F14" s="10">
+        <v>9</v>
+      </c>
+      <c r="F14" s="9">
         <v>19</v>
       </c>
-      <c r="G14" s="11">
+      <c r="G14" s="10">
         <v>0</v>
       </c>
       <c r="H14" s="8">
         <v>0</v>
       </c>
-      <c r="I14" s="9">
+      <c r="I14" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="K14" s="31">
+        <v>9</v>
+      </c>
+      <c r="K14" s="30">
         <v>4</v>
       </c>
       <c r="L14" s="8">
         <v>0</v>
       </c>
-      <c r="M14" s="29" t="s">
-        <v>25</v>
-      </c>
-      <c r="N14" s="32">
+      <c r="M14" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="N14" s="31">
         <v>19</v>
       </c>
       <c r="O14" s="8">
         <v>0</v>
       </c>
-      <c r="P14" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="U14" s="44"/>
+      <c r="P14" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="U14" s="43"/>
       <c r="V14">
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
     </row>
     <row r="15" spans="1:22">
-      <c r="A15" s="10">
+      <c r="A15" s="9">
         <v>5</v>
       </c>
       <c r="B15" s="7">
@@ -2045,217 +1474,217 @@
       <c r="C15" s="8">
         <v>0</v>
       </c>
-      <c r="D15" s="9">
+      <c r="D15" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F15" s="10">
+        <v>9</v>
+      </c>
+      <c r="F15" s="9">
         <v>20</v>
       </c>
-      <c r="G15" s="11">
+      <c r="G15" s="10">
         <v>0</v>
       </c>
       <c r="H15" s="8">
         <v>0</v>
       </c>
-      <c r="I15" s="9">
+      <c r="I15" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J15" s="45" t="s">
-        <v>12</v>
-      </c>
-      <c r="K15" s="31">
+      <c r="J15" s="44" t="s">
+        <v>9</v>
+      </c>
+      <c r="K15" s="30">
         <v>5</v>
       </c>
       <c r="L15" s="8">
         <v>0</v>
       </c>
-      <c r="M15" s="29" t="s">
-        <v>25</v>
-      </c>
-      <c r="N15" s="32">
+      <c r="M15" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="N15" s="31">
         <v>20</v>
       </c>
       <c r="O15" s="8">
         <v>0</v>
       </c>
-      <c r="P15" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="U15" s="44"/>
+      <c r="P15" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="U15" s="43"/>
       <c r="V15">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:22">
-      <c r="A16" s="10">
+      <c r="A16" s="9">
         <v>6</v>
       </c>
-      <c r="B16" s="12">
+      <c r="B16" s="11">
         <v>0</v>
       </c>
       <c r="C16" s="8">
         <v>0</v>
       </c>
-      <c r="D16" s="9">
+      <c r="D16" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F16" s="10">
-        <v>21</v>
-      </c>
-      <c r="G16" s="11">
+        <v>9</v>
+      </c>
+      <c r="F16" s="9">
+        <v>21</v>
+      </c>
+      <c r="G16" s="10">
         <v>0</v>
       </c>
       <c r="H16" s="8">
         <v>0</v>
       </c>
-      <c r="I16" s="9">
+      <c r="I16" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="K16" s="31">
+        <v>9</v>
+      </c>
+      <c r="K16" s="30">
         <v>6</v>
       </c>
       <c r="L16" s="8">
         <v>0</v>
       </c>
-      <c r="M16" s="29" t="s">
-        <v>25</v>
-      </c>
-      <c r="N16" s="32">
+      <c r="M16" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="N16" s="31">
         <v>21</v>
       </c>
       <c r="O16" s="8">
         <v>0</v>
       </c>
-      <c r="P16" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="U16" s="44"/>
+      <c r="P16" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="U16" s="43"/>
       <c r="V16">
         <f t="shared" si="2"/>
         <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:22">
-      <c r="A17" s="10">
+      <c r="A17" s="9">
         <v>7</v>
       </c>
-      <c r="B17" s="12">
+      <c r="B17" s="11">
         <v>0</v>
       </c>
       <c r="C17" s="8">
         <v>0</v>
       </c>
-      <c r="D17" s="9">
+      <c r="D17" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F17" s="10">
+        <v>9</v>
+      </c>
+      <c r="F17" s="9">
         <v>22</v>
       </c>
-      <c r="G17" s="11">
+      <c r="G17" s="10">
         <v>0</v>
       </c>
       <c r="H17" s="8">
         <v>0</v>
       </c>
-      <c r="I17" s="9">
+      <c r="I17" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J17" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="K17" s="31">
+        <v>9</v>
+      </c>
+      <c r="K17" s="30">
         <v>7</v>
       </c>
       <c r="L17" s="8">
         <v>0</v>
       </c>
-      <c r="M17" s="29" t="s">
-        <v>25</v>
-      </c>
-      <c r="N17" s="32">
+      <c r="M17" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="N17" s="31">
         <v>22</v>
       </c>
       <c r="O17" s="8">
         <v>0</v>
       </c>
-      <c r="P17" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="U17" s="44"/>
+      <c r="P17" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="U17" s="43"/>
       <c r="V17">
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
     </row>
     <row r="18" spans="1:22">
-      <c r="A18" s="10">
+      <c r="A18" s="9">
         <v>8</v>
       </c>
-      <c r="B18" s="12">
+      <c r="B18" s="11">
         <v>0</v>
       </c>
       <c r="C18" s="8">
         <v>0</v>
       </c>
-      <c r="D18" s="9">
+      <c r="D18" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F18" s="10">
+        <v>9</v>
+      </c>
+      <c r="F18" s="9">
         <v>23</v>
       </c>
-      <c r="G18" s="11">
+      <c r="G18" s="10">
         <v>0</v>
       </c>
       <c r="H18" s="8">
         <v>0</v>
       </c>
-      <c r="I18" s="9">
+      <c r="I18" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J18" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="K18" s="31">
+        <v>9</v>
+      </c>
+      <c r="K18" s="30">
         <v>8</v>
       </c>
       <c r="L18" s="8">
         <v>0</v>
       </c>
-      <c r="M18" s="29" t="s">
-        <v>25</v>
-      </c>
-      <c r="N18" s="32">
+      <c r="M18" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="N18" s="31">
         <v>23</v>
       </c>
       <c r="O18" s="8">
         <v>0</v>
       </c>
-      <c r="P18" s="11" t="s">
-        <v>25</v>
+      <c r="P18" s="10" t="s">
+        <v>21</v>
       </c>
       <c r="V18">
         <f t="shared" si="2"/>
@@ -2263,55 +1692,55 @@
       </c>
     </row>
     <row r="19" spans="1:22">
-      <c r="A19" s="10">
-        <v>9</v>
-      </c>
-      <c r="B19" s="12">
+      <c r="A19" s="9">
+        <v>9</v>
+      </c>
+      <c r="B19" s="11">
         <v>0</v>
       </c>
       <c r="C19" s="8">
         <v>0</v>
       </c>
-      <c r="D19" s="9">
+      <c r="D19" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F19" s="10">
+        <v>9</v>
+      </c>
+      <c r="F19" s="9">
         <v>24</v>
       </c>
-      <c r="G19" s="11">
+      <c r="G19" s="10">
         <v>0</v>
       </c>
       <c r="H19" s="8">
         <v>0</v>
       </c>
-      <c r="I19" s="9">
+      <c r="I19" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J19" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="K19" s="31">
+        <v>9</v>
+      </c>
+      <c r="K19" s="30">
         <v>9</v>
       </c>
       <c r="L19" s="8">
         <v>0</v>
       </c>
-      <c r="M19" s="29" t="s">
-        <v>25</v>
-      </c>
-      <c r="N19" s="32">
+      <c r="M19" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="N19" s="31">
         <v>24</v>
       </c>
       <c r="O19" s="8">
         <v>0</v>
       </c>
-      <c r="P19" s="11" t="s">
-        <v>25</v>
+      <c r="P19" s="10" t="s">
+        <v>21</v>
       </c>
       <c r="V19">
         <f t="shared" si="2"/>
@@ -2319,55 +1748,55 @@
       </c>
     </row>
     <row r="20" spans="1:22">
-      <c r="A20" s="10">
+      <c r="A20" s="9">
         <v>10</v>
       </c>
-      <c r="B20" s="12">
+      <c r="B20" s="11">
         <v>0</v>
       </c>
       <c r="C20" s="8">
         <v>0</v>
       </c>
-      <c r="D20" s="9">
+      <c r="D20" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F20" s="10">
+        <v>9</v>
+      </c>
+      <c r="F20" s="9">
         <v>25</v>
       </c>
-      <c r="G20" s="11">
+      <c r="G20" s="10">
         <v>0</v>
       </c>
       <c r="H20" s="8">
         <v>0</v>
       </c>
-      <c r="I20" s="9">
+      <c r="I20" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J20" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="K20" s="31">
+        <v>9</v>
+      </c>
+      <c r="K20" s="30">
         <v>10</v>
       </c>
       <c r="L20" s="8">
         <v>0</v>
       </c>
-      <c r="M20" s="29" t="s">
+      <c r="M20" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="N20" s="31">
         <v>25</v>
       </c>
-      <c r="N20" s="32">
-        <v>25</v>
-      </c>
       <c r="O20" s="8">
         <v>0</v>
       </c>
-      <c r="P20" s="11" t="s">
-        <v>25</v>
+      <c r="P20" s="10" t="s">
+        <v>21</v>
       </c>
       <c r="V20">
         <f t="shared" si="2"/>
@@ -2375,55 +1804,55 @@
       </c>
     </row>
     <row r="21" spans="1:22">
-      <c r="A21" s="10">
+      <c r="A21" s="9">
         <v>11</v>
       </c>
-      <c r="B21" s="12">
+      <c r="B21" s="11">
         <v>0</v>
       </c>
       <c r="C21" s="8">
         <v>0</v>
       </c>
-      <c r="D21" s="9">
+      <c r="D21" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F21" s="10">
+        <v>9</v>
+      </c>
+      <c r="F21" s="9">
         <v>26</v>
       </c>
-      <c r="G21" s="11">
+      <c r="G21" s="10">
         <v>0</v>
       </c>
       <c r="H21" s="8">
         <v>0</v>
       </c>
-      <c r="I21" s="9">
+      <c r="I21" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J21" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="K21" s="31">
+        <v>9</v>
+      </c>
+      <c r="K21" s="30">
         <v>11</v>
       </c>
       <c r="L21" s="8">
         <v>0</v>
       </c>
-      <c r="M21" s="29" t="s">
-        <v>25</v>
-      </c>
-      <c r="N21" s="32">
+      <c r="M21" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="N21" s="31">
         <v>26</v>
       </c>
       <c r="O21" s="8">
         <v>0</v>
       </c>
-      <c r="P21" s="11" t="s">
-        <v>25</v>
+      <c r="P21" s="10" t="s">
+        <v>21</v>
       </c>
       <c r="V21">
         <f t="shared" si="2"/>
@@ -2431,55 +1860,55 @@
       </c>
     </row>
     <row r="22" spans="1:22">
-      <c r="A22" s="10">
+      <c r="A22" s="9">
         <v>12</v>
       </c>
-      <c r="B22" s="12">
+      <c r="B22" s="11">
         <v>0</v>
       </c>
       <c r="C22" s="8">
         <v>0</v>
       </c>
-      <c r="D22" s="9">
+      <c r="D22" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="E22" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F22" s="9">
+        <v>27</v>
+      </c>
+      <c r="G22" s="10">
+        <v>0</v>
+      </c>
+      <c r="H22" s="8">
+        <v>0</v>
+      </c>
+      <c r="I22" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J22" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="K22" s="30">
         <v>12</v>
       </c>
-      <c r="F22" s="10">
+      <c r="L22" s="8">
+        <v>0</v>
+      </c>
+      <c r="M22" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="N22" s="31">
         <v>27</v>
       </c>
-      <c r="G22" s="11">
-        <v>0</v>
-      </c>
-      <c r="H22" s="8">
-        <v>0</v>
-      </c>
-      <c r="I22" s="9">
-        <f>IF(H22="TTU",G22,G22+H22)</f>
-        <v>0</v>
-      </c>
-      <c r="J22" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="K22" s="31">
-        <v>12</v>
-      </c>
-      <c r="L22" s="8">
-        <v>0</v>
-      </c>
-      <c r="M22" s="29" t="s">
-        <v>25</v>
-      </c>
-      <c r="N22" s="32">
-        <v>27</v>
-      </c>
       <c r="O22" s="8">
         <v>0</v>
       </c>
-      <c r="P22" s="11" t="s">
-        <v>25</v>
+      <c r="P22" s="10" t="s">
+        <v>21</v>
       </c>
       <c r="V22">
         <f t="shared" si="2"/>
@@ -2487,55 +1916,55 @@
       </c>
     </row>
     <row r="23" spans="1:22">
-      <c r="A23" s="10">
+      <c r="A23" s="9">
         <v>13</v>
       </c>
-      <c r="B23" s="12">
+      <c r="B23" s="11">
         <v>0</v>
       </c>
       <c r="C23" s="8">
         <v>0</v>
       </c>
-      <c r="D23" s="9">
+      <c r="D23" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F23" s="10">
+        <v>9</v>
+      </c>
+      <c r="F23" s="9">
         <v>28</v>
       </c>
-      <c r="G23" s="11">
+      <c r="G23" s="10">
         <v>0</v>
       </c>
       <c r="H23" s="8">
         <v>0</v>
       </c>
-      <c r="I23" s="9">
+      <c r="I23" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J23" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="K23" s="31">
+        <v>9</v>
+      </c>
+      <c r="K23" s="30">
         <v>13</v>
       </c>
       <c r="L23" s="8">
         <v>0</v>
       </c>
-      <c r="M23" s="29" t="s">
-        <v>25</v>
-      </c>
-      <c r="N23" s="32">
+      <c r="M23" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="N23" s="31">
         <v>28</v>
       </c>
       <c r="O23" s="8">
         <v>0</v>
       </c>
-      <c r="P23" s="33" t="s">
-        <v>25</v>
+      <c r="P23" s="32" t="s">
+        <v>21</v>
       </c>
       <c r="V23">
         <f t="shared" si="2"/>
@@ -2543,55 +1972,55 @@
       </c>
     </row>
     <row r="24" spans="1:22">
-      <c r="A24" s="10">
+      <c r="A24" s="9">
         <v>14</v>
       </c>
-      <c r="B24" s="12">
+      <c r="B24" s="11">
         <v>0</v>
       </c>
       <c r="C24" s="8">
         <v>0</v>
       </c>
-      <c r="D24" s="9">
+      <c r="D24" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F24" s="10">
+        <v>9</v>
+      </c>
+      <c r="F24" s="9">
         <v>29</v>
       </c>
-      <c r="G24" s="11">
+      <c r="G24" s="10">
         <v>0</v>
       </c>
       <c r="H24" s="8">
         <v>0</v>
       </c>
-      <c r="I24" s="9">
+      <c r="I24" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J24" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="K24" s="31">
+        <v>9</v>
+      </c>
+      <c r="K24" s="30">
         <v>14</v>
       </c>
       <c r="L24" s="8">
         <v>0</v>
       </c>
-      <c r="M24" s="29" t="s">
-        <v>25</v>
-      </c>
-      <c r="N24" s="32">
+      <c r="M24" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="N24" s="31">
         <v>29</v>
       </c>
       <c r="O24" s="8">
         <v>0</v>
       </c>
-      <c r="P24" s="11" t="s">
-        <v>25</v>
+      <c r="P24" s="10" t="s">
+        <v>21</v>
       </c>
       <c r="V24">
         <f t="shared" si="2"/>
@@ -2599,55 +2028,55 @@
       </c>
     </row>
     <row r="25" spans="1:22">
-      <c r="A25" s="10">
+      <c r="A25" s="9">
         <v>15</v>
       </c>
-      <c r="B25" s="12">
+      <c r="B25" s="11">
         <v>0</v>
       </c>
       <c r="C25" s="8">
         <v>0</v>
       </c>
-      <c r="D25" s="9">
+      <c r="D25" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E25" s="45" t="s">
-        <v>12</v>
-      </c>
-      <c r="F25" s="10">
+      <c r="E25" s="44" t="s">
+        <v>9</v>
+      </c>
+      <c r="F25" s="9">
         <v>30</v>
       </c>
-      <c r="G25" s="11">
+      <c r="G25" s="10">
         <v>0</v>
       </c>
       <c r="H25" s="8">
         <v>0</v>
       </c>
-      <c r="I25" s="9">
+      <c r="I25" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J25" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="K25" s="31">
+        <v>9</v>
+      </c>
+      <c r="K25" s="30">
         <v>15</v>
       </c>
       <c r="L25" s="8">
         <v>0</v>
       </c>
-      <c r="M25" s="29" t="s">
-        <v>25</v>
-      </c>
-      <c r="N25" s="32">
+      <c r="M25" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="N25" s="31">
         <v>30</v>
       </c>
       <c r="O25" s="8">
         <v>0</v>
       </c>
-      <c r="P25" s="11" t="s">
-        <v>25</v>
+      <c r="P25" s="10" t="s">
+        <v>21</v>
       </c>
       <c r="V25">
         <f t="shared" si="2"/>
@@ -2655,111 +2084,111 @@
       </c>
     </row>
     <row r="26" spans="1:22">
-      <c r="A26" s="13"/>
-      <c r="B26" s="14"/>
-      <c r="C26" s="15"/>
+      <c r="A26" s="12"/>
+      <c r="B26" s="13"/>
+      <c r="C26" s="14"/>
       <c r="D26" s="8"/>
-      <c r="E26" s="13"/>
-      <c r="F26" s="10">
+      <c r="E26" s="12"/>
+      <c r="F26" s="9">
         <v>31</v>
       </c>
-      <c r="G26" s="11">
+      <c r="G26" s="10">
         <v>0</v>
       </c>
       <c r="H26" s="8">
         <v>0</v>
       </c>
-      <c r="I26" s="9">
+      <c r="I26" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J26" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="K26" s="34"/>
-      <c r="L26" s="14"/>
-      <c r="M26" s="35"/>
-      <c r="N26" s="32">
+        <v>9</v>
+      </c>
+      <c r="K26" s="33"/>
+      <c r="L26" s="13"/>
+      <c r="M26" s="34"/>
+      <c r="N26" s="31">
         <v>31</v>
       </c>
       <c r="O26" s="8">
         <v>0</v>
       </c>
-      <c r="P26" s="11" t="s">
-        <v>25</v>
+      <c r="P26" s="10" t="s">
+        <v>21</v>
       </c>
       <c r="V26">
         <f t="shared" ref="V26:V41" si="3">IF(OR(H11&gt;=1,H11="TTU"),0,V25+1)</f>
         <v>16</v>
       </c>
     </row>
-    <row r="27" ht="13.5" customHeight="1" spans="1:22">
-      <c r="A27" s="16"/>
-      <c r="B27" s="17"/>
-      <c r="C27" s="18"/>
-      <c r="D27" s="18"/>
-      <c r="E27" s="16"/>
-      <c r="F27" s="16"/>
-      <c r="G27" s="18"/>
-      <c r="H27" s="18"/>
-      <c r="I27" s="18"/>
-      <c r="J27" s="16"/>
-      <c r="K27" s="36"/>
-      <c r="L27" s="17"/>
-      <c r="M27" s="37"/>
-      <c r="N27" s="38"/>
-      <c r="O27" s="17"/>
-      <c r="P27" s="18"/>
+    <row r="27" spans="1:22" ht="13.5" customHeight="1">
+      <c r="A27" s="15"/>
+      <c r="B27" s="16"/>
+      <c r="C27" s="17"/>
+      <c r="D27" s="17"/>
+      <c r="E27" s="15"/>
+      <c r="F27" s="15"/>
+      <c r="G27" s="17"/>
+      <c r="H27" s="17"/>
+      <c r="I27" s="17"/>
+      <c r="J27" s="15"/>
+      <c r="K27" s="35"/>
+      <c r="L27" s="16"/>
+      <c r="M27" s="36"/>
+      <c r="N27" s="37"/>
+      <c r="O27" s="16"/>
+      <c r="P27" s="17"/>
       <c r="V27">
         <f t="shared" si="3"/>
         <v>17</v>
       </c>
     </row>
-    <row r="28" ht="13.5" spans="1:22">
-      <c r="A28" s="19" t="s">
-        <v>26</v>
-      </c>
-      <c r="B28" s="20">
+    <row r="28" spans="1:22">
+      <c r="A28" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="B28" s="19">
         <f>SUM(B11:B25)</f>
         <v>0</v>
       </c>
-      <c r="C28" s="20">
+      <c r="C28" s="19">
         <f>SUM(C11:C25)</f>
         <v>0</v>
       </c>
-      <c r="D28" s="20">
+      <c r="D28" s="19">
         <f>SUM(D11:D25)</f>
         <v>0</v>
       </c>
-      <c r="E28" s="21"/>
-      <c r="F28" s="19" t="s">
-        <v>26</v>
-      </c>
-      <c r="G28" s="20">
+      <c r="E28" s="20"/>
+      <c r="F28" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="G28" s="19">
         <f>SUM(G11:G26)</f>
         <v>0</v>
       </c>
-      <c r="H28" s="20">
+      <c r="H28" s="19">
         <f>SUM(H11:H26)</f>
         <v>0</v>
       </c>
-      <c r="I28" s="20">
+      <c r="I28" s="19">
         <f>SUM(I11:I26)</f>
         <v>0</v>
       </c>
-      <c r="J28" s="21"/>
-      <c r="K28" s="39"/>
-      <c r="L28" s="40"/>
-      <c r="M28" s="41"/>
-      <c r="N28" s="42"/>
-      <c r="O28" s="40"/>
-      <c r="P28" s="43"/>
+      <c r="J28" s="20"/>
+      <c r="K28" s="38"/>
+      <c r="L28" s="39"/>
+      <c r="M28" s="40"/>
+      <c r="N28" s="41"/>
+      <c r="O28" s="39"/>
+      <c r="P28" s="42"/>
       <c r="V28">
         <f t="shared" si="3"/>
         <v>18</v>
       </c>
     </row>
-    <row r="29" ht="13.5" spans="16:22">
+    <row r="29" spans="1:22">
       <c r="P29" s="2"/>
       <c r="V29">
         <f t="shared" si="3"/>
@@ -2768,10 +2197,10 @@
     </row>
     <row r="30" spans="1:22">
       <c r="A30" s="2" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C30" s="2"/>
       <c r="P30" s="2"/>
@@ -2782,11 +2211,11 @@
     </row>
     <row r="31" spans="1:22">
       <c r="A31" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B31" s="22"/>
-      <c r="C31" s="23"/>
-      <c r="D31" s="24">
+        <v>25</v>
+      </c>
+      <c r="B31" s="21"/>
+      <c r="C31" s="22"/>
+      <c r="D31" s="23">
         <f>C28+H28</f>
         <v>0</v>
       </c>
@@ -2798,24 +2227,24 @@
     </row>
     <row r="32" spans="1:22">
       <c r="A32" s="2" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B32" s="2"/>
-      <c r="C32" s="25"/>
-      <c r="D32" s="24">
+      <c r="C32" s="24"/>
+      <c r="D32" s="23">
         <f>D28+I28</f>
         <v>0</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="G32" s="2"/>
       <c r="H32" s="2"/>
       <c r="I32" s="2"/>
       <c r="J32" s="2"/>
       <c r="K32" s="2" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="L32" s="2"/>
       <c r="M32" s="2"/>
@@ -2829,24 +2258,24 @@
     </row>
     <row r="33" spans="1:22">
       <c r="A33" s="2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B33" s="2"/>
-      <c r="C33" s="23"/>
-      <c r="D33" s="26">
+      <c r="C33" s="22"/>
+      <c r="D33" s="25">
         <f>COUNTIF(C11:C25,"&gt;0")+COUNTIF(C11:C25,"TTU")+COUNTIF(H11:H26,"&gt;0")+COUNTIF(H11:H26,"TTU")</f>
         <v>0</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" s="2" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G33" s="2"/>
       <c r="H33" s="2"/>
       <c r="I33" s="2"/>
       <c r="J33" s="2"/>
       <c r="K33" s="2" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="L33" s="2"/>
       <c r="M33" s="2"/>
@@ -2860,22 +2289,22 @@
     </row>
     <row r="34" spans="1:22">
       <c r="A34" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D34" s="26">
+        <v>32</v>
+      </c>
+      <c r="D34" s="25">
         <f>V41</f>
         <v>31</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" s="2" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="G34" s="2"/>
       <c r="H34" s="2"/>
       <c r="I34" s="2"/>
       <c r="J34" s="2"/>
       <c r="K34" s="2" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="L34" s="2"/>
       <c r="M34" s="2"/>
@@ -2888,21 +2317,21 @@
     </row>
     <row r="35" spans="1:22">
       <c r="A35" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D35" s="26">
+        <v>35</v>
+      </c>
+      <c r="D35" s="25">
         <f>MAX(V11:V41)</f>
         <v>31</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="G35" s="2"/>
       <c r="H35" s="2"/>
       <c r="I35" s="2"/>
       <c r="J35" s="2"/>
-      <c r="K35" s="46" t="s">
-        <v>41</v>
+      <c r="K35" s="45" t="s">
+        <v>37</v>
       </c>
       <c r="L35" s="2"/>
       <c r="M35" s="2"/>
@@ -2913,46 +2342,49 @@
         <v>25</v>
       </c>
     </row>
-    <row r="36" spans="22:22">
+    <row r="36" spans="1:22">
       <c r="V36">
         <f t="shared" si="3"/>
         <v>26</v>
       </c>
     </row>
-    <row r="37" spans="22:22">
+    <row r="37" spans="1:22">
       <c r="V37">
         <f t="shared" si="3"/>
         <v>27</v>
       </c>
     </row>
-    <row r="38" spans="22:22">
+    <row r="38" spans="1:22">
       <c r="V38">
         <f t="shared" si="3"/>
         <v>28</v>
       </c>
     </row>
-    <row r="39" spans="22:22">
+    <row r="39" spans="1:22">
       <c r="V39">
         <f t="shared" si="3"/>
         <v>29</v>
       </c>
     </row>
-    <row r="40" spans="22:22">
+    <row r="40" spans="1:22">
       <c r="V40">
         <f t="shared" si="3"/>
         <v>30</v>
       </c>
     </row>
-    <row r="41" spans="22:22">
+    <row r="41" spans="1:22">
       <c r="V41">
         <f t="shared" si="3"/>
         <v>31</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="M5:M6"/>
+    <mergeCell ref="M7:M8"/>
+  </mergeCells>
   <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="landscape" horizontalDpi="360" verticalDpi="360"/>
-  <headerFooter/>
+  <pageMargins left="0.25138888888888899" right="0.25138888888888899" top="0.75138888888888899" bottom="0.75138888888888899" header="0.29861111111111099" footer="0.29861111111111099"/>
+  <pageSetup paperSize="9" scale="97" orientation="landscape" verticalDpi="360" r:id="rId1"/>
 </worksheet>
 </file>
--- a/TEMPLATE PENGUAPAN.xlsx
+++ b/TEMPLATE PENGUAPAN.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24332"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zavie\Downloads\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41B26B0C-91BD-42FA-825D-B222DCD9888E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="28125" windowHeight="12495"/>
   </bookViews>
   <sheets>
     <sheet name="Penguapan" sheetId="1" r:id="rId1"/>
@@ -21,7 +15,7 @@
     <definedName name="NONA">#REF!</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">Penguapan!$A$1:$P$35</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
@@ -40,9 +34,21 @@
     <t>:  2026</t>
   </si>
   <si>
+    <t>STASIUN PENGUAPAN NO.</t>
+  </si>
+  <si>
+    <t>:  049</t>
+  </si>
+  <si>
     <t>BULAN</t>
   </si>
   <si>
+    <t>STASIUN HUJAN NO.</t>
+  </si>
+  <si>
+    <t>:  461</t>
+  </si>
+  <si>
     <t>TEMPAT PEMERIKSAAN</t>
   </si>
   <si>
@@ -55,42 +61,60 @@
     <t>:  Kambera</t>
   </si>
   <si>
+    <t>PEMERIKSAAN PENGUAPAN</t>
+  </si>
+  <si>
+    <t>: 08.00</t>
+  </si>
+  <si>
+    <t>KABUPATEN</t>
+  </si>
+  <si>
+    <t>:  Sumba Timur</t>
+  </si>
+  <si>
+    <t>TIAP PAGI JAM</t>
+  </si>
+  <si>
+    <t>PROPINSI</t>
+  </si>
+  <si>
+    <t>:  Nusa Tenggara Timur</t>
+  </si>
+  <si>
+    <t>JIKA TAK ADA HUJAN</t>
+  </si>
+  <si>
+    <t>: 0</t>
+  </si>
+  <si>
+    <t>KOLOM HUJAN DIISI  :</t>
+  </si>
+  <si>
+    <t>Tanggal Pengukuran</t>
+  </si>
+  <si>
+    <t>Beda tinggi H dalam mm</t>
+  </si>
+  <si>
+    <t>Hujan P dalam mm</t>
+  </si>
+  <si>
+    <t>Penguapan  E = P + H dalam mm</t>
+  </si>
+  <si>
+    <t>Jam</t>
+  </si>
+  <si>
+    <t>Kecep. Angin (KM)</t>
+  </si>
+  <si>
+    <t>Suhu Air (oC)</t>
+  </si>
+  <si>
     <t>08.00</t>
   </si>
   <si>
-    <t>KABUPATEN</t>
-  </si>
-  <si>
-    <t>:  Sumba Timur</t>
-  </si>
-  <si>
-    <t>PROPINSI</t>
-  </si>
-  <si>
-    <t>:  Nusa Tenggara Timur</t>
-  </si>
-  <si>
-    <t>Tanggal Pengukuran</t>
-  </si>
-  <si>
-    <t>Beda tinggi H dalam mm</t>
-  </si>
-  <si>
-    <t>Hujan P dalam mm</t>
-  </si>
-  <si>
-    <t>Penguapan  E = P + H dalam mm</t>
-  </si>
-  <si>
-    <t>Jam</t>
-  </si>
-  <si>
-    <t>Kecep. Angin (KM)</t>
-  </si>
-  <si>
-    <t>Suhu Air (oC)</t>
-  </si>
-  <si>
     <t>-</t>
   </si>
   <si>
@@ -140,46 +164,20 @@
   </si>
   <si>
     <t>//// = Air dalam panci penguapan meluap karena hujan sedang - lebat</t>
-  </si>
-  <si>
-    <t>:  049</t>
-  </si>
-  <si>
-    <t>STASIUN PENGUAPAN NO.</t>
-  </si>
-  <si>
-    <t>STASIUN HUJAN NO.</t>
-  </si>
-  <si>
-    <t>:  461</t>
-  </si>
-  <si>
-    <t>: 08.00</t>
-  </si>
-  <si>
-    <t>PEMERIKSAAN PENGUAPAN</t>
-  </si>
-  <si>
-    <t>TIAP PAGI JAM</t>
-  </si>
-  <si>
-    <t>JIKA TAK ADA HUJAN</t>
-  </si>
-  <si>
-    <t>KOLOM HUJAN DIISI  :</t>
-  </si>
-  <si>
-    <t>: 0</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="166" formatCode="0.0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="5">
+    <numFmt numFmtId="176" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;Rp&quot;* #,##0_-;\-&quot;Rp&quot;* #,##0_-;_-&quot;Rp&quot;* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;Rp&quot;* #,##0.00_-;\-&quot;Rp&quot;* #,##0.00_-;_-&quot;Rp&quot;* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="180" formatCode="0.0"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="25">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -203,25 +201,357 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="8"/>
       <name val="Arial"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="8"/>
-      <name val="Arial"/>
-      <family val="2"/>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="28">
+  <borders count="36">
     <border>
       <left/>
       <right/>
@@ -310,9 +640,7 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
+      <left/>
       <right style="thin">
         <color auto="1"/>
       </right>
@@ -325,7 +653,9 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
       <right style="thin">
         <color auto="1"/>
       </right>
@@ -584,136 +914,416 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="30" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="32" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="33" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="34" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="35" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="8" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="8" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="8" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="1" fillId="0" borderId="4" xfId="8" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="1" fillId="0" borderId="5" xfId="8" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="8" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="8" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="8" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="8" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="8" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="8" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="2" fillId="0" borderId="13" xfId="8" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="8" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="180" fontId="3" fillId="0" borderId="0" xfId="8" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="8" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" indent="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="2" fillId="0" borderId="0" xfId="8" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="8" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="8" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="8" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="8" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="8" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="8" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="8"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="1" fillId="0" borderId="15" xfId="8" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" indent="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="1" fillId="0" borderId="8" xfId="8" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="1" fillId="0" borderId="19" xfId="8" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="8" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="8" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="8" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="8" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="8" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="8" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="8" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="8" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="8" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="8" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="8" applyFont="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="50">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal_Sheet1" xfId="1" xr:uid="{00000000-0005-0000-0000-000008000000}"/>
+    <cellStyle name="40% - Accent1" xfId="1" builtinId="31"/>
+    <cellStyle name="Comma" xfId="2" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="3" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="4" builtinId="7"/>
+    <cellStyle name="Currency" xfId="5" builtinId="4"/>
+    <cellStyle name="Percent" xfId="6" builtinId="5"/>
+    <cellStyle name="Hyperlink" xfId="7" builtinId="8"/>
+    <cellStyle name="Normal_Sheet1" xfId="8"/>
+    <cellStyle name="60% - Accent4" xfId="9" builtinId="44"/>
+    <cellStyle name="Followed Hyperlink" xfId="10" builtinId="9"/>
+    <cellStyle name="Check Cell" xfId="11" builtinId="23"/>
+    <cellStyle name="Heading 2" xfId="12" builtinId="17"/>
+    <cellStyle name="Note" xfId="13" builtinId="10"/>
+    <cellStyle name="40% - Accent3" xfId="14" builtinId="39"/>
+    <cellStyle name="Warning Text" xfId="15" builtinId="11"/>
+    <cellStyle name="40% - Accent2" xfId="16" builtinId="35"/>
+    <cellStyle name="Title" xfId="17" builtinId="15"/>
+    <cellStyle name="CExplanatory Text" xfId="18" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="19" builtinId="16"/>
+    <cellStyle name="Heading 3" xfId="20" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="21" builtinId="19"/>
+    <cellStyle name="Input" xfId="22" builtinId="20"/>
+    <cellStyle name="60% - Accent3" xfId="23" builtinId="40"/>
+    <cellStyle name="Good" xfId="24" builtinId="26"/>
+    <cellStyle name="Output" xfId="25" builtinId="21"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="Calculation" xfId="27" builtinId="22"/>
+    <cellStyle name="Linked Cell" xfId="28" builtinId="24"/>
+    <cellStyle name="Total" xfId="29" builtinId="25"/>
+    <cellStyle name="Bad" xfId="30" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="31" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="32" builtinId="29"/>
+    <cellStyle name="20% - Accent5" xfId="33" builtinId="46"/>
+    <cellStyle name="60% - Accent1" xfId="34" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="35" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="36" builtinId="34"/>
+    <cellStyle name="20% - Accent6" xfId="37" builtinId="50"/>
+    <cellStyle name="60% - Accent2" xfId="38" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="39" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="40" builtinId="38"/>
+    <cellStyle name="Accent4" xfId="41" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="42" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="43" builtinId="43"/>
+    <cellStyle name="Accent5" xfId="44" builtinId="45"/>
+    <cellStyle name="40% - Accent5" xfId="45" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="46" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="47" builtinId="49"/>
+    <cellStyle name="40% - Accent6" xfId="48" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="49" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -971,37 +1581,36 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:V41"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="11.28515625" customWidth="1"/>
-    <col min="4" max="4" width="10.5703125" customWidth="1"/>
-    <col min="5" max="5" width="5.85546875" customWidth="1"/>
-    <col min="6" max="6" width="11.42578125" customWidth="1"/>
-    <col min="9" max="9" width="10.5703125" customWidth="1"/>
-    <col min="10" max="10" width="6.42578125" customWidth="1"/>
-    <col min="11" max="11" width="11.42578125" customWidth="1"/>
-    <col min="12" max="12" width="7.85546875" customWidth="1"/>
-    <col min="15" max="15" width="7.85546875" customWidth="1"/>
-    <col min="19" max="19" width="12.85546875" customWidth="1"/>
+    <col min="1" max="1" width="11.2857142857143" customWidth="1"/>
+    <col min="4" max="4" width="10.5714285714286" customWidth="1"/>
+    <col min="5" max="5" width="5.85714285714286" customWidth="1"/>
+    <col min="6" max="6" width="11.4285714285714" customWidth="1"/>
+    <col min="9" max="9" width="10.5714285714286" customWidth="1"/>
+    <col min="10" max="10" width="6.42857142857143" customWidth="1"/>
+    <col min="11" max="11" width="11.4285714285714" customWidth="1"/>
+    <col min="12" max="12" width="7.85714285714286" customWidth="1"/>
+    <col min="15" max="15" width="7.85714285714286" customWidth="1"/>
+    <col min="19" max="19" width="12.8571428571429" customWidth="1"/>
     <col min="22" max="22" width="53" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22">
+    <row r="1" spans="22:22">
       <c r="V1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:22">
+    <row r="2" spans="1:16">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -1017,53 +1626,53 @@
       </c>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
-      <c r="J2" s="46" t="s">
-        <v>39</v>
+      <c r="J2" s="24" t="s">
+        <v>4</v>
       </c>
       <c r="K2" s="2"/>
       <c r="L2" s="2"/>
-      <c r="M2" s="47" t="s">
-        <v>38</v>
+      <c r="M2" s="25" t="s">
+        <v>5</v>
       </c>
       <c r="N2" s="2"/>
       <c r="O2" s="2"/>
       <c r="P2" s="2"/>
     </row>
-    <row r="3" spans="1:22">
+    <row r="3" spans="1:16">
       <c r="A3" s="3"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
       <c r="E3" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
-      <c r="J3" s="46" t="s">
-        <v>40</v>
+      <c r="J3" s="24" t="s">
+        <v>7</v>
       </c>
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
-      <c r="M3" s="47" t="s">
-        <v>41</v>
+      <c r="M3" s="25" t="s">
+        <v>8</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
       <c r="P3" s="2"/>
     </row>
-    <row r="4" spans="1:22">
+    <row r="4" spans="1:16">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
       <c r="E4" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F4" s="2"/>
       <c r="G4" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
@@ -1075,83 +1684,83 @@
       <c r="O4" s="2"/>
       <c r="P4" s="2"/>
     </row>
-    <row r="5" spans="1:22" ht="12.75" customHeight="1">
+    <row r="5" customHeight="1" spans="1:16">
       <c r="A5" s="3"/>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
       <c r="E5" s="1" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
-      <c r="J5" s="50" t="s">
-        <v>43</v>
-      </c>
-      <c r="K5" s="49"/>
-      <c r="L5" s="49"/>
-      <c r="M5" s="48" t="s">
-        <v>42</v>
-      </c>
-      <c r="N5" s="47"/>
+      <c r="J5" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="K5" s="27"/>
+      <c r="L5" s="27"/>
+      <c r="M5" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="N5" s="25"/>
       <c r="O5" s="2"/>
       <c r="P5" s="2"/>
     </row>
-    <row r="6" spans="1:22">
+    <row r="6" spans="1:16">
       <c r="A6" s="3"/>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
       <c r="D6" s="3"/>
       <c r="E6" s="1" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F6" s="2"/>
       <c r="G6" s="2" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
-      <c r="J6" s="50" t="s">
-        <v>44</v>
-      </c>
-      <c r="K6" s="49"/>
-      <c r="L6" s="49"/>
-      <c r="M6" s="48"/>
-      <c r="N6" s="47"/>
+      <c r="J6" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="K6" s="27"/>
+      <c r="L6" s="27"/>
+      <c r="M6" s="25"/>
+      <c r="N6" s="25"/>
       <c r="O6" s="2"/>
       <c r="P6" s="2"/>
     </row>
-    <row r="7" spans="1:22">
+    <row r="7" spans="1:16">
       <c r="A7" s="3"/>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
       <c r="E7" s="1" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F7" s="2"/>
       <c r="G7" s="2" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
-      <c r="J7" s="50" t="s">
-        <v>45</v>
-      </c>
-      <c r="K7" s="26"/>
+      <c r="J7" s="26" t="s">
+        <v>20</v>
+      </c>
+      <c r="K7" s="28"/>
       <c r="L7" s="2"/>
-      <c r="M7" s="48" t="s">
-        <v>47</v>
-      </c>
-      <c r="N7" s="47"/>
+      <c r="M7" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="N7" s="25"/>
       <c r="O7" s="2"/>
       <c r="P7" s="2"/>
     </row>
-    <row r="8" spans="1:22">
+    <row r="8" spans="1:16">
       <c r="A8" s="3"/>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -1161,17 +1770,17 @@
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
       <c r="I8" s="3"/>
-      <c r="J8" s="50" t="s">
-        <v>46</v>
+      <c r="J8" s="26" t="s">
+        <v>22</v>
       </c>
       <c r="K8" s="3"/>
       <c r="L8" s="3"/>
-      <c r="M8" s="48"/>
+      <c r="M8" s="25"/>
       <c r="N8" s="3"/>
       <c r="O8" s="3"/>
       <c r="P8" s="3"/>
     </row>
-    <row r="9" spans="1:22" ht="13.5" customHeight="1">
+    <row r="9" ht="13.5" customHeight="1" spans="1:16">
       <c r="A9" s="3"/>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
@@ -1189,54 +1798,54 @@
       <c r="O9" s="3"/>
       <c r="P9" s="3"/>
     </row>
-    <row r="10" spans="1:22" ht="35.25" customHeight="1">
+    <row r="10" ht="35.25" customHeight="1" spans="1:16">
       <c r="A10" s="4" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="L10" s="4" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="M10" s="4" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="N10" s="4" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="O10" s="4" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="P10" s="4" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -1246,49 +1855,49 @@
       <c r="B11" s="7">
         <v>0</v>
       </c>
-      <c r="C11" s="8">
+      <c r="C11" s="7">
         <v>0</v>
       </c>
       <c r="D11" s="8">
-        <f t="shared" ref="D11:D25" si="0">IF(C11="TTU",B11,B11+C11)</f>
-        <v>0</v>
-      </c>
-      <c r="E11" s="44" t="s">
-        <v>9</v>
+        <f t="shared" ref="D11:D25" si="0">IF(OR(B11=8888,B11=9999,B11="-",C11=8888,C11=9999,C11="-"),"0,0",IF(OR(C11="TTU",C11=""),B11,B11+C11))</f>
+        <v>0</v>
+      </c>
+      <c r="E11" s="47" t="s">
+        <v>30</v>
       </c>
       <c r="F11" s="6">
         <v>16</v>
       </c>
-      <c r="G11" s="8">
-        <v>0</v>
-      </c>
-      <c r="H11" s="8">
+      <c r="G11" s="7">
+        <v>0</v>
+      </c>
+      <c r="H11" s="7">
         <v>0</v>
       </c>
       <c r="I11" s="8">
-        <f t="shared" ref="I11:I26" si="1">IF(H11="TTU",G11,G11+H11)</f>
+        <f t="shared" ref="I11:I26" si="1">IF(OR(G11=8888,G11=9999,G11="-",H11=8888,H11=9999,H11="-"),"0,0",IF(OR(H11="TTU",H11=""),G11,G11+H11))</f>
         <v>0</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="K11" s="27">
+        <v>30</v>
+      </c>
+      <c r="K11" s="29">
         <v>1</v>
       </c>
       <c r="L11" s="8">
         <v>0</v>
       </c>
-      <c r="M11" s="28" t="s">
-        <v>21</v>
-      </c>
-      <c r="N11" s="29">
+      <c r="M11" s="30" t="s">
+        <v>31</v>
+      </c>
+      <c r="N11" s="31">
         <v>16</v>
       </c>
       <c r="O11" s="8">
         <v>0</v>
       </c>
       <c r="P11" s="8" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="V11">
         <f>IF(OR(C11&gt;=1,C11="TTU"),0,1)</f>
@@ -1302,7 +1911,7 @@
       <c r="B12" s="7">
         <v>0</v>
       </c>
-      <c r="C12" s="8">
+      <c r="C12" s="7">
         <v>0</v>
       </c>
       <c r="D12" s="8">
@@ -1310,15 +1919,15 @@
         <v>0</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="F12" s="9">
         <v>17</v>
       </c>
-      <c r="G12" s="10">
-        <v>0</v>
-      </c>
-      <c r="H12" s="8">
+      <c r="G12" s="7">
+        <v>0</v>
+      </c>
+      <c r="H12" s="7">
         <v>0</v>
       </c>
       <c r="I12" s="8">
@@ -1326,25 +1935,25 @@
         <v>0</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="K12" s="30">
+        <v>30</v>
+      </c>
+      <c r="K12" s="32">
         <v>2</v>
       </c>
       <c r="L12" s="8">
         <v>0</v>
       </c>
-      <c r="M12" s="28" t="s">
-        <v>21</v>
-      </c>
-      <c r="N12" s="31">
+      <c r="M12" s="30" t="s">
+        <v>31</v>
+      </c>
+      <c r="N12" s="33">
         <v>17</v>
       </c>
       <c r="O12" s="8">
         <v>0</v>
       </c>
-      <c r="P12" s="10" t="s">
-        <v>21</v>
+      <c r="P12" s="34" t="s">
+        <v>31</v>
       </c>
       <c r="V12">
         <f t="shared" ref="V12:V25" si="2">IF(OR(C12&gt;=1,C12="TTU"),0,V11+1)</f>
@@ -1358,7 +1967,7 @@
       <c r="B13" s="7">
         <v>0</v>
       </c>
-      <c r="C13" s="8">
+      <c r="C13" s="7">
         <v>0</v>
       </c>
       <c r="D13" s="8">
@@ -1366,15 +1975,15 @@
         <v>0</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="F13" s="9">
         <v>18</v>
       </c>
-      <c r="G13" s="10">
-        <v>0</v>
-      </c>
-      <c r="H13" s="8">
+      <c r="G13" s="7">
+        <v>0</v>
+      </c>
+      <c r="H13" s="7">
         <v>0</v>
       </c>
       <c r="I13" s="8">
@@ -1382,25 +1991,25 @@
         <v>0</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="K13" s="30">
+        <v>30</v>
+      </c>
+      <c r="K13" s="32">
         <v>3</v>
       </c>
       <c r="L13" s="8">
         <v>0</v>
       </c>
-      <c r="M13" s="28" t="s">
-        <v>21</v>
-      </c>
-      <c r="N13" s="31">
+      <c r="M13" s="30" t="s">
+        <v>31</v>
+      </c>
+      <c r="N13" s="33">
         <v>18</v>
       </c>
       <c r="O13" s="8">
         <v>0</v>
       </c>
-      <c r="P13" s="10" t="s">
-        <v>21</v>
+      <c r="P13" s="34" t="s">
+        <v>31</v>
       </c>
       <c r="V13">
         <f t="shared" si="2"/>
@@ -1414,7 +2023,7 @@
       <c r="B14" s="7">
         <v>0</v>
       </c>
-      <c r="C14" s="8">
+      <c r="C14" s="7">
         <v>0</v>
       </c>
       <c r="D14" s="8">
@@ -1422,15 +2031,15 @@
         <v>0</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="F14" s="9">
         <v>19</v>
       </c>
-      <c r="G14" s="10">
-        <v>0</v>
-      </c>
-      <c r="H14" s="8">
+      <c r="G14" s="7">
+        <v>0</v>
+      </c>
+      <c r="H14" s="7">
         <v>0</v>
       </c>
       <c r="I14" s="8">
@@ -1438,27 +2047,27 @@
         <v>0</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="K14" s="30">
+        <v>30</v>
+      </c>
+      <c r="K14" s="32">
         <v>4</v>
       </c>
       <c r="L14" s="8">
         <v>0</v>
       </c>
-      <c r="M14" s="28" t="s">
-        <v>21</v>
-      </c>
-      <c r="N14" s="31">
+      <c r="M14" s="30" t="s">
+        <v>31</v>
+      </c>
+      <c r="N14" s="33">
         <v>19</v>
       </c>
       <c r="O14" s="8">
         <v>0</v>
       </c>
-      <c r="P14" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="U14" s="43"/>
+      <c r="P14" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="U14" s="46"/>
       <c r="V14">
         <f t="shared" si="2"/>
         <v>4</v>
@@ -1471,7 +2080,7 @@
       <c r="B15" s="7">
         <v>0</v>
       </c>
-      <c r="C15" s="8">
+      <c r="C15" s="7">
         <v>0</v>
       </c>
       <c r="D15" s="8">
@@ -1479,43 +2088,43 @@
         <v>0</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="F15" s="9">
         <v>20</v>
       </c>
-      <c r="G15" s="10">
-        <v>0</v>
-      </c>
-      <c r="H15" s="8">
+      <c r="G15" s="7">
+        <v>0</v>
+      </c>
+      <c r="H15" s="7">
         <v>0</v>
       </c>
       <c r="I15" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J15" s="44" t="s">
-        <v>9</v>
-      </c>
-      <c r="K15" s="30">
+      <c r="J15" s="47" t="s">
+        <v>30</v>
+      </c>
+      <c r="K15" s="32">
         <v>5</v>
       </c>
       <c r="L15" s="8">
         <v>0</v>
       </c>
-      <c r="M15" s="28" t="s">
-        <v>21</v>
-      </c>
-      <c r="N15" s="31">
+      <c r="M15" s="30" t="s">
+        <v>31</v>
+      </c>
+      <c r="N15" s="33">
         <v>20</v>
       </c>
       <c r="O15" s="8">
         <v>0</v>
       </c>
-      <c r="P15" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="U15" s="43"/>
+      <c r="P15" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="U15" s="46"/>
       <c r="V15">
         <f t="shared" si="2"/>
         <v>5</v>
@@ -1525,10 +2134,10 @@
       <c r="A16" s="9">
         <v>6</v>
       </c>
-      <c r="B16" s="11">
-        <v>0</v>
-      </c>
-      <c r="C16" s="8">
+      <c r="B16" s="7">
+        <v>0</v>
+      </c>
+      <c r="C16" s="7">
         <v>0</v>
       </c>
       <c r="D16" s="8">
@@ -1536,15 +2145,15 @@
         <v>0</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="F16" s="9">
         <v>21</v>
       </c>
-      <c r="G16" s="10">
-        <v>0</v>
-      </c>
-      <c r="H16" s="8">
+      <c r="G16" s="7">
+        <v>0</v>
+      </c>
+      <c r="H16" s="7">
         <v>0</v>
       </c>
       <c r="I16" s="8">
@@ -1552,27 +2161,27 @@
         <v>0</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="K16" s="30">
+        <v>30</v>
+      </c>
+      <c r="K16" s="32">
         <v>6</v>
       </c>
       <c r="L16" s="8">
         <v>0</v>
       </c>
-      <c r="M16" s="28" t="s">
+      <c r="M16" s="30" t="s">
+        <v>31</v>
+      </c>
+      <c r="N16" s="33">
         <v>21</v>
       </c>
-      <c r="N16" s="31">
-        <v>21</v>
-      </c>
       <c r="O16" s="8">
         <v>0</v>
       </c>
-      <c r="P16" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="U16" s="43"/>
+      <c r="P16" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="U16" s="46"/>
       <c r="V16">
         <f t="shared" si="2"/>
         <v>6</v>
@@ -1582,10 +2191,10 @@
       <c r="A17" s="9">
         <v>7</v>
       </c>
-      <c r="B17" s="11">
-        <v>0</v>
-      </c>
-      <c r="C17" s="8">
+      <c r="B17" s="7">
+        <v>0</v>
+      </c>
+      <c r="C17" s="7">
         <v>0</v>
       </c>
       <c r="D17" s="8">
@@ -1593,15 +2202,15 @@
         <v>0</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="F17" s="9">
         <v>22</v>
       </c>
-      <c r="G17" s="10">
-        <v>0</v>
-      </c>
-      <c r="H17" s="8">
+      <c r="G17" s="7">
+        <v>0</v>
+      </c>
+      <c r="H17" s="7">
         <v>0</v>
       </c>
       <c r="I17" s="8">
@@ -1609,27 +2218,27 @@
         <v>0</v>
       </c>
       <c r="J17" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="K17" s="30">
+        <v>30</v>
+      </c>
+      <c r="K17" s="32">
         <v>7</v>
       </c>
       <c r="L17" s="8">
         <v>0</v>
       </c>
-      <c r="M17" s="28" t="s">
-        <v>21</v>
-      </c>
-      <c r="N17" s="31">
+      <c r="M17" s="30" t="s">
+        <v>31</v>
+      </c>
+      <c r="N17" s="33">
         <v>22</v>
       </c>
       <c r="O17" s="8">
         <v>0</v>
       </c>
-      <c r="P17" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="U17" s="43"/>
+      <c r="P17" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="U17" s="46"/>
       <c r="V17">
         <f t="shared" si="2"/>
         <v>7</v>
@@ -1639,10 +2248,10 @@
       <c r="A18" s="9">
         <v>8</v>
       </c>
-      <c r="B18" s="11">
-        <v>0</v>
-      </c>
-      <c r="C18" s="8">
+      <c r="B18" s="7">
+        <v>0</v>
+      </c>
+      <c r="C18" s="7">
         <v>0</v>
       </c>
       <c r="D18" s="8">
@@ -1650,15 +2259,15 @@
         <v>0</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="F18" s="9">
         <v>23</v>
       </c>
-      <c r="G18" s="10">
-        <v>0</v>
-      </c>
-      <c r="H18" s="8">
+      <c r="G18" s="7">
+        <v>0</v>
+      </c>
+      <c r="H18" s="7">
         <v>0</v>
       </c>
       <c r="I18" s="8">
@@ -1666,25 +2275,25 @@
         <v>0</v>
       </c>
       <c r="J18" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="K18" s="30">
+        <v>30</v>
+      </c>
+      <c r="K18" s="32">
         <v>8</v>
       </c>
       <c r="L18" s="8">
         <v>0</v>
       </c>
-      <c r="M18" s="28" t="s">
-        <v>21</v>
-      </c>
-      <c r="N18" s="31">
+      <c r="M18" s="30" t="s">
+        <v>31</v>
+      </c>
+      <c r="N18" s="33">
         <v>23</v>
       </c>
       <c r="O18" s="8">
         <v>0</v>
       </c>
-      <c r="P18" s="10" t="s">
-        <v>21</v>
+      <c r="P18" s="34" t="s">
+        <v>31</v>
       </c>
       <c r="V18">
         <f t="shared" si="2"/>
@@ -1695,10 +2304,10 @@
       <c r="A19" s="9">
         <v>9</v>
       </c>
-      <c r="B19" s="11">
-        <v>0</v>
-      </c>
-      <c r="C19" s="8">
+      <c r="B19" s="7">
+        <v>0</v>
+      </c>
+      <c r="C19" s="7">
         <v>0</v>
       </c>
       <c r="D19" s="8">
@@ -1706,15 +2315,15 @@
         <v>0</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="F19" s="9">
         <v>24</v>
       </c>
-      <c r="G19" s="10">
-        <v>0</v>
-      </c>
-      <c r="H19" s="8">
+      <c r="G19" s="7">
+        <v>0</v>
+      </c>
+      <c r="H19" s="7">
         <v>0</v>
       </c>
       <c r="I19" s="8">
@@ -1722,25 +2331,25 @@
         <v>0</v>
       </c>
       <c r="J19" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="K19" s="32">
         <v>9</v>
       </c>
-      <c r="K19" s="30">
-        <v>9</v>
-      </c>
       <c r="L19" s="8">
         <v>0</v>
       </c>
-      <c r="M19" s="28" t="s">
-        <v>21</v>
-      </c>
-      <c r="N19" s="31">
+      <c r="M19" s="30" t="s">
+        <v>31</v>
+      </c>
+      <c r="N19" s="33">
         <v>24</v>
       </c>
       <c r="O19" s="8">
         <v>0</v>
       </c>
-      <c r="P19" s="10" t="s">
-        <v>21</v>
+      <c r="P19" s="34" t="s">
+        <v>31</v>
       </c>
       <c r="V19">
         <f t="shared" si="2"/>
@@ -1751,10 +2360,10 @@
       <c r="A20" s="9">
         <v>10</v>
       </c>
-      <c r="B20" s="11">
-        <v>0</v>
-      </c>
-      <c r="C20" s="8">
+      <c r="B20" s="7">
+        <v>0</v>
+      </c>
+      <c r="C20" s="7">
         <v>0</v>
       </c>
       <c r="D20" s="8">
@@ -1762,15 +2371,15 @@
         <v>0</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="F20" s="9">
         <v>25</v>
       </c>
-      <c r="G20" s="10">
-        <v>0</v>
-      </c>
-      <c r="H20" s="8">
+      <c r="G20" s="7">
+        <v>0</v>
+      </c>
+      <c r="H20" s="7">
         <v>0</v>
       </c>
       <c r="I20" s="8">
@@ -1778,25 +2387,25 @@
         <v>0</v>
       </c>
       <c r="J20" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="K20" s="30">
+        <v>30</v>
+      </c>
+      <c r="K20" s="32">
         <v>10</v>
       </c>
       <c r="L20" s="8">
         <v>0</v>
       </c>
-      <c r="M20" s="28" t="s">
-        <v>21</v>
-      </c>
-      <c r="N20" s="31">
+      <c r="M20" s="30" t="s">
+        <v>31</v>
+      </c>
+      <c r="N20" s="33">
         <v>25</v>
       </c>
       <c r="O20" s="8">
         <v>0</v>
       </c>
-      <c r="P20" s="10" t="s">
-        <v>21</v>
+      <c r="P20" s="34" t="s">
+        <v>31</v>
       </c>
       <c r="V20">
         <f t="shared" si="2"/>
@@ -1807,10 +2416,10 @@
       <c r="A21" s="9">
         <v>11</v>
       </c>
-      <c r="B21" s="11">
-        <v>0</v>
-      </c>
-      <c r="C21" s="8">
+      <c r="B21" s="7">
+        <v>0</v>
+      </c>
+      <c r="C21" s="7">
         <v>0</v>
       </c>
       <c r="D21" s="8">
@@ -1818,15 +2427,15 @@
         <v>0</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="F21" s="9">
         <v>26</v>
       </c>
-      <c r="G21" s="10">
-        <v>0</v>
-      </c>
-      <c r="H21" s="8">
+      <c r="G21" s="7">
+        <v>0</v>
+      </c>
+      <c r="H21" s="7">
         <v>0</v>
       </c>
       <c r="I21" s="8">
@@ -1834,25 +2443,25 @@
         <v>0</v>
       </c>
       <c r="J21" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="K21" s="30">
+        <v>30</v>
+      </c>
+      <c r="K21" s="32">
         <v>11</v>
       </c>
       <c r="L21" s="8">
         <v>0</v>
       </c>
-      <c r="M21" s="28" t="s">
-        <v>21</v>
-      </c>
-      <c r="N21" s="31">
+      <c r="M21" s="30" t="s">
+        <v>31</v>
+      </c>
+      <c r="N21" s="33">
         <v>26</v>
       </c>
       <c r="O21" s="8">
         <v>0</v>
       </c>
-      <c r="P21" s="10" t="s">
-        <v>21</v>
+      <c r="P21" s="34" t="s">
+        <v>31</v>
       </c>
       <c r="V21">
         <f t="shared" si="2"/>
@@ -1863,10 +2472,10 @@
       <c r="A22" s="9">
         <v>12</v>
       </c>
-      <c r="B22" s="11">
-        <v>0</v>
-      </c>
-      <c r="C22" s="8">
+      <c r="B22" s="7">
+        <v>0</v>
+      </c>
+      <c r="C22" s="7">
         <v>0</v>
       </c>
       <c r="D22" s="8">
@@ -1874,15 +2483,15 @@
         <v>0</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="F22" s="9">
         <v>27</v>
       </c>
-      <c r="G22" s="10">
-        <v>0</v>
-      </c>
-      <c r="H22" s="8">
+      <c r="G22" s="7">
+        <v>0</v>
+      </c>
+      <c r="H22" s="7">
         <v>0</v>
       </c>
       <c r="I22" s="8">
@@ -1890,25 +2499,25 @@
         <v>0</v>
       </c>
       <c r="J22" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="K22" s="30">
+        <v>30</v>
+      </c>
+      <c r="K22" s="32">
         <v>12</v>
       </c>
       <c r="L22" s="8">
         <v>0</v>
       </c>
-      <c r="M22" s="28" t="s">
-        <v>21</v>
-      </c>
-      <c r="N22" s="31">
+      <c r="M22" s="30" t="s">
+        <v>31</v>
+      </c>
+      <c r="N22" s="33">
         <v>27</v>
       </c>
       <c r="O22" s="8">
         <v>0</v>
       </c>
-      <c r="P22" s="10" t="s">
-        <v>21</v>
+      <c r="P22" s="34" t="s">
+        <v>31</v>
       </c>
       <c r="V22">
         <f t="shared" si="2"/>
@@ -1919,10 +2528,10 @@
       <c r="A23" s="9">
         <v>13</v>
       </c>
-      <c r="B23" s="11">
-        <v>0</v>
-      </c>
-      <c r="C23" s="8">
+      <c r="B23" s="7">
+        <v>0</v>
+      </c>
+      <c r="C23" s="7">
         <v>0</v>
       </c>
       <c r="D23" s="8">
@@ -1930,15 +2539,15 @@
         <v>0</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="F23" s="9">
         <v>28</v>
       </c>
-      <c r="G23" s="10">
-        <v>0</v>
-      </c>
-      <c r="H23" s="8">
+      <c r="G23" s="7">
+        <v>0</v>
+      </c>
+      <c r="H23" s="7">
         <v>0</v>
       </c>
       <c r="I23" s="8">
@@ -1946,25 +2555,25 @@
         <v>0</v>
       </c>
       <c r="J23" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="K23" s="30">
+        <v>30</v>
+      </c>
+      <c r="K23" s="32">
         <v>13</v>
       </c>
       <c r="L23" s="8">
         <v>0</v>
       </c>
-      <c r="M23" s="28" t="s">
-        <v>21</v>
-      </c>
-      <c r="N23" s="31">
+      <c r="M23" s="30" t="s">
+        <v>31</v>
+      </c>
+      <c r="N23" s="33">
         <v>28</v>
       </c>
       <c r="O23" s="8">
         <v>0</v>
       </c>
-      <c r="P23" s="32" t="s">
-        <v>21</v>
+      <c r="P23" s="35" t="s">
+        <v>31</v>
       </c>
       <c r="V23">
         <f t="shared" si="2"/>
@@ -1975,10 +2584,10 @@
       <c r="A24" s="9">
         <v>14</v>
       </c>
-      <c r="B24" s="11">
-        <v>0</v>
-      </c>
-      <c r="C24" s="8">
+      <c r="B24" s="7">
+        <v>0</v>
+      </c>
+      <c r="C24" s="7">
         <v>0</v>
       </c>
       <c r="D24" s="8">
@@ -1986,15 +2595,15 @@
         <v>0</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="F24" s="9">
         <v>29</v>
       </c>
-      <c r="G24" s="10">
-        <v>0</v>
-      </c>
-      <c r="H24" s="8">
+      <c r="G24" s="7">
+        <v>0</v>
+      </c>
+      <c r="H24" s="7">
         <v>0</v>
       </c>
       <c r="I24" s="8">
@@ -2002,25 +2611,25 @@
         <v>0</v>
       </c>
       <c r="J24" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="K24" s="30">
+        <v>30</v>
+      </c>
+      <c r="K24" s="32">
         <v>14</v>
       </c>
       <c r="L24" s="8">
         <v>0</v>
       </c>
-      <c r="M24" s="28" t="s">
-        <v>21</v>
-      </c>
-      <c r="N24" s="31">
+      <c r="M24" s="30" t="s">
+        <v>31</v>
+      </c>
+      <c r="N24" s="33">
         <v>29</v>
       </c>
       <c r="O24" s="8">
         <v>0</v>
       </c>
-      <c r="P24" s="10" t="s">
-        <v>21</v>
+      <c r="P24" s="34" t="s">
+        <v>31</v>
       </c>
       <c r="V24">
         <f t="shared" si="2"/>
@@ -2031,26 +2640,26 @@
       <c r="A25" s="9">
         <v>15</v>
       </c>
-      <c r="B25" s="11">
-        <v>0</v>
-      </c>
-      <c r="C25" s="8">
+      <c r="B25" s="7">
+        <v>0</v>
+      </c>
+      <c r="C25" s="7">
         <v>0</v>
       </c>
       <c r="D25" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E25" s="44" t="s">
-        <v>9</v>
+      <c r="E25" s="47" t="s">
+        <v>30</v>
       </c>
       <c r="F25" s="9">
         <v>30</v>
       </c>
-      <c r="G25" s="10">
-        <v>0</v>
-      </c>
-      <c r="H25" s="8">
+      <c r="G25" s="7">
+        <v>0</v>
+      </c>
+      <c r="H25" s="7">
         <v>0</v>
       </c>
       <c r="I25" s="8">
@@ -2058,25 +2667,25 @@
         <v>0</v>
       </c>
       <c r="J25" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="K25" s="30">
+        <v>30</v>
+      </c>
+      <c r="K25" s="32">
         <v>15</v>
       </c>
       <c r="L25" s="8">
         <v>0</v>
       </c>
-      <c r="M25" s="28" t="s">
-        <v>21</v>
-      </c>
-      <c r="N25" s="31">
+      <c r="M25" s="30" t="s">
+        <v>31</v>
+      </c>
+      <c r="N25" s="33">
         <v>30</v>
       </c>
       <c r="O25" s="8">
         <v>0</v>
       </c>
-      <c r="P25" s="10" t="s">
-        <v>21</v>
+      <c r="P25" s="34" t="s">
+        <v>31</v>
       </c>
       <c r="V25">
         <f t="shared" si="2"/>
@@ -2084,18 +2693,18 @@
       </c>
     </row>
     <row r="26" spans="1:22">
-      <c r="A26" s="12"/>
-      <c r="B26" s="13"/>
-      <c r="C26" s="14"/>
+      <c r="A26" s="10"/>
+      <c r="B26" s="11"/>
+      <c r="C26" s="12"/>
       <c r="D26" s="8"/>
-      <c r="E26" s="12"/>
+      <c r="E26" s="10"/>
       <c r="F26" s="9">
         <v>31</v>
       </c>
-      <c r="G26" s="10">
-        <v>0</v>
-      </c>
-      <c r="H26" s="8">
+      <c r="G26" s="7">
+        <v>0</v>
+      </c>
+      <c r="H26" s="7">
         <v>0</v>
       </c>
       <c r="I26" s="8">
@@ -2103,92 +2712,92 @@
         <v>0</v>
       </c>
       <c r="J26" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="K26" s="33"/>
-      <c r="L26" s="13"/>
-      <c r="M26" s="34"/>
-      <c r="N26" s="31">
+        <v>30</v>
+      </c>
+      <c r="K26" s="36"/>
+      <c r="L26" s="11"/>
+      <c r="M26" s="37"/>
+      <c r="N26" s="33">
         <v>31</v>
       </c>
       <c r="O26" s="8">
         <v>0</v>
       </c>
-      <c r="P26" s="10" t="s">
-        <v>21</v>
+      <c r="P26" s="34" t="s">
+        <v>31</v>
       </c>
       <c r="V26">
         <f t="shared" ref="V26:V41" si="3">IF(OR(H11&gt;=1,H11="TTU"),0,V25+1)</f>
         <v>16</v>
       </c>
     </row>
-    <row r="27" spans="1:22" ht="13.5" customHeight="1">
-      <c r="A27" s="15"/>
-      <c r="B27" s="16"/>
-      <c r="C27" s="17"/>
-      <c r="D27" s="17"/>
-      <c r="E27" s="15"/>
-      <c r="F27" s="15"/>
-      <c r="G27" s="17"/>
-      <c r="H27" s="17"/>
-      <c r="I27" s="17"/>
-      <c r="J27" s="15"/>
-      <c r="K27" s="35"/>
-      <c r="L27" s="16"/>
-      <c r="M27" s="36"/>
-      <c r="N27" s="37"/>
-      <c r="O27" s="16"/>
-      <c r="P27" s="17"/>
+    <row r="27" ht="13.5" customHeight="1" spans="1:22">
+      <c r="A27" s="13"/>
+      <c r="B27" s="14"/>
+      <c r="C27" s="15"/>
+      <c r="D27" s="15"/>
+      <c r="E27" s="13"/>
+      <c r="F27" s="13"/>
+      <c r="G27" s="15"/>
+      <c r="H27" s="15"/>
+      <c r="I27" s="15"/>
+      <c r="J27" s="13"/>
+      <c r="K27" s="38"/>
+      <c r="L27" s="14"/>
+      <c r="M27" s="39"/>
+      <c r="N27" s="40"/>
+      <c r="O27" s="14"/>
+      <c r="P27" s="15"/>
       <c r="V27">
         <f t="shared" si="3"/>
         <v>17</v>
       </c>
     </row>
-    <row r="28" spans="1:22">
-      <c r="A28" s="18" t="s">
-        <v>22</v>
-      </c>
-      <c r="B28" s="19">
-        <f>SUM(B11:B25)</f>
-        <v>0</v>
-      </c>
-      <c r="C28" s="19">
-        <f>SUM(C11:C25)</f>
-        <v>0</v>
-      </c>
-      <c r="D28" s="19">
-        <f>SUM(D11:D25)</f>
-        <v>0</v>
-      </c>
-      <c r="E28" s="20"/>
-      <c r="F28" s="18" t="s">
-        <v>22</v>
-      </c>
-      <c r="G28" s="19">
-        <f>SUM(G11:G26)</f>
-        <v>0</v>
-      </c>
-      <c r="H28" s="19">
-        <f>SUM(H11:H26)</f>
-        <v>0</v>
-      </c>
-      <c r="I28" s="19">
-        <f>SUM(I11:I26)</f>
-        <v>0</v>
-      </c>
-      <c r="J28" s="20"/>
-      <c r="K28" s="38"/>
-      <c r="L28" s="39"/>
-      <c r="M28" s="40"/>
-      <c r="N28" s="41"/>
-      <c r="O28" s="39"/>
-      <c r="P28" s="42"/>
+    <row r="28" ht="13.5" spans="1:22">
+      <c r="A28" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="B28" s="17">
+        <f t="shared" ref="B28:I28" si="4">SUMIFS(B11:B26,B11:B26,"&lt;&gt;9999",B11:B26,"&lt;&gt;8888")</f>
+        <v>0</v>
+      </c>
+      <c r="C28" s="17">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="D28" s="17">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="E28" s="18"/>
+      <c r="F28" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="G28" s="17">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H28" s="17">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="I28" s="17">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J28" s="18"/>
+      <c r="K28" s="41"/>
+      <c r="L28" s="42"/>
+      <c r="M28" s="43"/>
+      <c r="N28" s="44"/>
+      <c r="O28" s="42"/>
+      <c r="P28" s="45"/>
       <c r="V28">
         <f t="shared" si="3"/>
         <v>18</v>
       </c>
     </row>
-    <row r="29" spans="1:22">
+    <row r="29" ht="13.5" spans="16:22">
       <c r="P29" s="2"/>
       <c r="V29">
         <f t="shared" si="3"/>
@@ -2197,10 +2806,10 @@
     </row>
     <row r="30" spans="1:22">
       <c r="A30" s="2" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="C30" s="2"/>
       <c r="P30" s="2"/>
@@ -2211,11 +2820,11 @@
     </row>
     <row r="31" spans="1:22">
       <c r="A31" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B31" s="21"/>
-      <c r="C31" s="22"/>
-      <c r="D31" s="23">
+        <v>35</v>
+      </c>
+      <c r="B31" s="19"/>
+      <c r="C31" s="20"/>
+      <c r="D31" s="21">
         <f>C28+H28</f>
         <v>0</v>
       </c>
@@ -2227,24 +2836,24 @@
     </row>
     <row r="32" spans="1:22">
       <c r="A32" s="2" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="B32" s="2"/>
-      <c r="C32" s="24"/>
-      <c r="D32" s="23">
+      <c r="C32" s="22"/>
+      <c r="D32" s="21">
         <f>D28+I28</f>
         <v>0</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" s="2" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="G32" s="2"/>
       <c r="H32" s="2"/>
       <c r="I32" s="2"/>
       <c r="J32" s="2"/>
       <c r="K32" s="2" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="L32" s="2"/>
       <c r="M32" s="2"/>
@@ -2258,24 +2867,24 @@
     </row>
     <row r="33" spans="1:22">
       <c r="A33" s="2" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="B33" s="2"/>
-      <c r="C33" s="22"/>
-      <c r="D33" s="25">
+      <c r="C33" s="20"/>
+      <c r="D33" s="23">
         <f>COUNTIF(C11:C25,"&gt;0")+COUNTIF(C11:C25,"TTU")+COUNTIF(H11:H26,"&gt;0")+COUNTIF(H11:H26,"TTU")</f>
         <v>0</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" s="2" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="G33" s="2"/>
       <c r="H33" s="2"/>
       <c r="I33" s="2"/>
       <c r="J33" s="2"/>
       <c r="K33" s="2" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="L33" s="2"/>
       <c r="M33" s="2"/>
@@ -2289,22 +2898,22 @@
     </row>
     <row r="34" spans="1:22">
       <c r="A34" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D34" s="25">
+        <v>42</v>
+      </c>
+      <c r="D34" s="23">
         <f>V41</f>
         <v>31</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" s="2" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="G34" s="2"/>
       <c r="H34" s="2"/>
       <c r="I34" s="2"/>
       <c r="J34" s="2"/>
       <c r="K34" s="2" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="L34" s="2"/>
       <c r="M34" s="2"/>
@@ -2317,21 +2926,21 @@
     </row>
     <row r="35" spans="1:22">
       <c r="A35" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D35" s="25">
+        <v>45</v>
+      </c>
+      <c r="D35" s="23">
         <f>MAX(V11:V41)</f>
         <v>31</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="G35" s="2"/>
       <c r="H35" s="2"/>
       <c r="I35" s="2"/>
       <c r="J35" s="2"/>
-      <c r="K35" s="45" t="s">
-        <v>37</v>
+      <c r="K35" s="48" t="s">
+        <v>47</v>
       </c>
       <c r="L35" s="2"/>
       <c r="M35" s="2"/>
@@ -2342,37 +2951,37 @@
         <v>25</v>
       </c>
     </row>
-    <row r="36" spans="1:22">
+    <row r="36" spans="22:22">
       <c r="V36">
         <f t="shared" si="3"/>
         <v>26</v>
       </c>
     </row>
-    <row r="37" spans="1:22">
+    <row r="37" spans="22:22">
       <c r="V37">
         <f t="shared" si="3"/>
         <v>27</v>
       </c>
     </row>
-    <row r="38" spans="1:22">
+    <row r="38" spans="22:22">
       <c r="V38">
         <f t="shared" si="3"/>
         <v>28</v>
       </c>
     </row>
-    <row r="39" spans="1:22">
+    <row r="39" spans="22:22">
       <c r="V39">
         <f t="shared" si="3"/>
         <v>29</v>
       </c>
     </row>
-    <row r="40" spans="1:22">
+    <row r="40" spans="22:22">
       <c r="V40">
         <f t="shared" si="3"/>
         <v>30</v>
       </c>
     </row>
-    <row r="41" spans="1:22">
+    <row r="41" spans="22:22">
       <c r="V41">
         <f t="shared" si="3"/>
         <v>31</v>
@@ -2384,7 +2993,8 @@
     <mergeCell ref="M7:M8"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.25138888888888899" right="0.25138888888888899" top="0.75138888888888899" bottom="0.75138888888888899" header="0.29861111111111099" footer="0.29861111111111099"/>
-  <pageSetup paperSize="9" scale="97" orientation="landscape" verticalDpi="360" r:id="rId1"/>
+  <pageMargins left="0.251388888888889" right="0.251388888888889" top="0.751388888888889" bottom="0.751388888888889" header="0.298611111111111" footer="0.298611111111111"/>
+  <pageSetup paperSize="9" scale="99" orientation="landscape" verticalDpi="360"/>
+  <headerFooter/>
 </worksheet>
 </file>